--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E274E9C2-8B6A-445E-8805-0B6E2B21FC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A385730-D6F7-40CA-BC5E-6A1147A06EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -722,7 +722,7 @@
         <v>24</v>
       </c>
       <c r="C18" s="2">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2">
         <v>40</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A385730-D6F7-40CA-BC5E-6A1147A06EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD1989-F288-4388-B974-364312547FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -646,7 +646,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>30020101</v>
+        <v>100201011</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>19</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>30020102</v>
+        <v>100201021</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>20</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>30020103</v>
+        <v>100201031</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>21</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92DD1989-F288-4388-B974-364312547FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93DBEC8-6A09-485A-AC26-F589F55B81DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,14 +104,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:3666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4666</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:8500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,6 +125,14 @@
   </si>
   <si>
     <t>tough_broke_value</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6667</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -512,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>12</v>
@@ -649,10 +649,10 @@
         <v>100201011</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2">
         <v>40</v>
@@ -663,10 +663,10 @@
         <v>100201021</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2">
         <v>40</v>
@@ -677,7 +677,7 @@
         <v>100201031</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="2">
         <v>85</v>
@@ -691,7 +691,7 @@
         <v>30030101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16" s="2">
         <v>33</v>
@@ -705,7 +705,7 @@
         <v>30030102</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C17" s="2">
         <v>53</v>
@@ -719,7 +719,7 @@
         <v>30030103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2">
         <v>17</v>
@@ -733,7 +733,7 @@
         <v>30030104</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C19" s="2">
         <v>40</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93DBEC8-6A09-485A-AC26-F589F55B81DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF49B428-1DAD-4AF6-A50A-7D63946CFF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -133,6 +133,18 @@
   </si>
   <si>
     <t>1:6667</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:10500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -183,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -193,6 +205,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -473,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1218,6 +1231,118 @@
         <v>40</v>
       </c>
     </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54">
+        <v>1001011</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="4">
+        <v>0</v>
+      </c>
+      <c r="D54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55">
+        <v>1001021</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="4">
+        <v>0</v>
+      </c>
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56">
+        <v>1002011</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="4">
+        <v>0</v>
+      </c>
+      <c r="D56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57">
+        <v>1002021</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="4">
+        <v>0</v>
+      </c>
+      <c r="D57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58">
+        <v>1004011</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C58" s="4">
+        <v>0</v>
+      </c>
+      <c r="D58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59">
+        <v>1004021</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="4">
+        <v>0</v>
+      </c>
+      <c r="D59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60">
+        <v>14001011</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C60" s="4">
+        <v>0</v>
+      </c>
+      <c r="D60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61">
+        <v>14001021</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF49B428-1DAD-4AF6-A50A-7D63946CFF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117857D9-CE9E-4DF1-B2D8-FCFF69534C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="30">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>14001011</v>
+        <v>3002011</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C60" s="4">
         <v>0</v>
@@ -1331,16 +1331,128 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61">
+        <v>3002021</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="4">
+        <v>0</v>
+      </c>
+      <c r="D61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62">
+        <v>14001011</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C62" s="4">
+        <v>0</v>
+      </c>
+      <c r="D62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63">
         <v>14001021</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B63" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="4">
-        <v>0</v>
-      </c>
-      <c r="D61" s="4">
-        <v>0</v>
+      <c r="C63" s="4">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64">
+        <v>100101011</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="4">
+        <v>50</v>
+      </c>
+      <c r="D64" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65">
+        <v>100101021</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="4">
+        <v>50</v>
+      </c>
+      <c r="D65" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66">
+        <v>100201011</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="4">
+        <v>50</v>
+      </c>
+      <c r="D66" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67">
+        <v>100201021</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="4">
+        <v>50</v>
+      </c>
+      <c r="D67" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68">
+        <v>100301011</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="4">
+        <v>50</v>
+      </c>
+      <c r="D68" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69">
+        <v>100301021</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="4">
+        <v>50</v>
+      </c>
+      <c r="D69" s="4">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117857D9-CE9E-4DF1-B2D8-FCFF69534C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE80504-54BA-46E0-B320-9FCEEC57F027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -145,6 +145,38 @@
   </si>
   <si>
     <t>1:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4500_2:4500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5000_2:5000_3:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6850_2:6850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5675_2:5675_3:5675_4:5675</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4320_2:4320_3:4320_4:4320_5:4320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4575_2:4575_3:4575_4:4575</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11700</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1320,7 +1352,7 @@
         <v>3002011</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C60" s="4">
         <v>0</v>
@@ -1334,7 +1366,7 @@
         <v>3002021</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C61" s="4">
         <v>0</v>
@@ -1376,10 +1408,10 @@
         <v>100101011</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C64" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D64" s="4">
         <v>40</v>
@@ -1390,10 +1422,10 @@
         <v>100101021</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C65" s="4">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D65" s="4">
         <v>40</v>
@@ -1404,10 +1436,10 @@
         <v>100201011</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C66" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D66" s="4">
         <v>40</v>
@@ -1418,10 +1450,10 @@
         <v>100201021</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C67" s="4">
         <v>18</v>
-      </c>
-      <c r="C67" s="4">
-        <v>50</v>
       </c>
       <c r="D67" s="4">
         <v>40</v>
@@ -1432,10 +1464,10 @@
         <v>100301011</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C68" s="4">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D68" s="4">
         <v>40</v>
@@ -1446,10 +1478,10 @@
         <v>100301021</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" s="4">
         <v>18</v>
-      </c>
-      <c r="C69" s="4">
-        <v>50</v>
       </c>
       <c r="D69" s="4">
         <v>40</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE80504-54BA-46E0-B320-9FCEEC57F027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD28872-AA07-42B2-A6C3-5DF18FF509F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="2310" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -136,18 +136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:10500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:4500_2:4500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,11 +160,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:7600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:11700</t>
+    <t>1:22300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:20000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:17300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:17700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:18000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1268,7 @@
         <v>1001011</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C54" s="4">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>1001021</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C55" s="4">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>1002011</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C56" s="4">
         <v>0</v>
@@ -1310,7 +1310,7 @@
         <v>1002021</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C57" s="4">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>1004011</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C58" s="4">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>1004021</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C59" s="4">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>3002011</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C60" s="4">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>14001011</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C62" s="4">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>14001021</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C63" s="4">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         <v>100101011</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C64" s="4">
         <v>35</v>
@@ -1422,7 +1422,7 @@
         <v>100101021</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C65" s="4">
         <v>23</v>
@@ -1436,7 +1436,7 @@
         <v>100201011</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C66" s="4">
         <v>35</v>
@@ -1450,7 +1450,7 @@
         <v>100201021</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C67" s="4">
         <v>18</v>
@@ -1464,7 +1464,7 @@
         <v>100301011</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C68" s="4">
         <v>14</v>
@@ -1478,7 +1478,7 @@
         <v>100301021</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C69" s="4">
         <v>18</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD28872-AA07-42B2-A6C3-5DF18FF509F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BF690D-EA47-4224-8729-0BD6E915859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="930" yWindow="1320" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -136,30 +136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4500_2:4500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5000_2:5000_3:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6850_2:6850</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5675_2:5675_3:5675_4:5675</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4320_2:4320_3:4320_4:4320_5:4320</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4575_2:4575_3:4575_4:4575</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:22300</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,6 +153,30 @@
   </si>
   <si>
     <t>1:18000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4200_2:4800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7500_2:10500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4500_2:7000_3:11800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4000_2:4000_3:6600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6000_2:4000_3:5100_4:5100_5:5100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4800_2:4800_3:8200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1268,7 @@
         <v>1001011</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C54" s="4">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>1001021</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C55" s="4">
         <v>0</v>
@@ -1296,7 +1296,7 @@
         <v>1002011</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C56" s="4">
         <v>0</v>
@@ -1310,7 +1310,7 @@
         <v>1002021</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C57" s="4">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>1004011</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C58" s="4">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>1004021</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C59" s="4">
         <v>0</v>
@@ -1352,7 +1352,7 @@
         <v>3002011</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C60" s="4">
         <v>0</v>
@@ -1366,7 +1366,7 @@
         <v>3002021</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C61" s="4">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>14001011</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C62" s="4">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>14001021</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C63" s="4">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         <v>100101011</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C64" s="4">
         <v>35</v>
@@ -1422,10 +1422,10 @@
         <v>100101021</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C65" s="4">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D65" s="4">
         <v>40</v>
@@ -1436,10 +1436,10 @@
         <v>100201011</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D66" s="4">
         <v>40</v>
@@ -1450,10 +1450,10 @@
         <v>100201021</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C67" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D67" s="4">
         <v>40</v>
@@ -1464,10 +1464,10 @@
         <v>100301011</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C68" s="4">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="4">
         <v>40</v>
@@ -1478,10 +1478,10 @@
         <v>100301021</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C69" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D69" s="4">
         <v>40</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BF690D-EA47-4224-8729-0BD6E915859F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE65784-9F0B-4406-A10E-37158DB8A2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="1320" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="37">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,27 +156,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4200_2:4800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7500_2:10500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4500_2:7000_3:11800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4000_2:4000_3:6600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6000_2:4000_3:5100_4:5100_5:5100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4800_2:4800_3:8200</t>
+    <t>1:4200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4200_2:4200_3:4200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -518,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1405,10 +1401,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>100101011</v>
+        <v>11101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C64" s="4">
         <v>35</v>
@@ -1419,10 +1415,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>100101021</v>
+        <v>11102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C65" s="4">
         <v>35</v>
@@ -1433,10 +1429,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>100201011</v>
+        <v>11201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C66" s="4">
         <v>24</v>
@@ -1447,10 +1443,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>100201021</v>
+        <v>11202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C67" s="4">
         <v>24</v>
@@ -1461,10 +1457,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>100301011</v>
+        <v>12101</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C68" s="4">
         <v>15</v>
@@ -1475,15 +1471,155 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>100301021</v>
+        <v>12102</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C69" s="4">
         <v>24</v>
       </c>
       <c r="D69" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70">
+        <v>12103</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="4">
+        <v>24</v>
+      </c>
+      <c r="D70" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71">
+        <v>12201</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="4">
+        <v>24</v>
+      </c>
+      <c r="D71" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72">
+        <v>12202</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="4">
+        <v>24</v>
+      </c>
+      <c r="D72" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73">
+        <v>12203</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C73" s="4">
+        <v>24</v>
+      </c>
+      <c r="D73" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74">
+        <v>13101</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C74" s="4">
+        <v>24</v>
+      </c>
+      <c r="D74" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75">
+        <v>13102</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C75" s="4">
+        <v>24</v>
+      </c>
+      <c r="D75" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76">
+        <v>13103</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C76" s="4">
+        <v>24</v>
+      </c>
+      <c r="D76" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77">
+        <v>13201</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C77" s="4">
+        <v>24</v>
+      </c>
+      <c r="D77" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78">
+        <v>13202</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C78" s="4">
+        <v>24</v>
+      </c>
+      <c r="D78" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79">
+        <v>13203</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C79" s="4">
+        <v>24</v>
+      </c>
+      <c r="D79" s="4">
         <v>40</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE65784-9F0B-4406-A10E-37158DB8A2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FB9BCA-483F-4821-9867-4C53C4B3B3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -156,10 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:4000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -172,7 +168,47 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4200_2:4200_3:4200</t>
+    <t>1:13400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5400_2:5000_3:5000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1404,7 +1440,7 @@
         <v>11101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C64" s="4">
         <v>35</v>
@@ -1418,7 +1454,7 @@
         <v>11102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="4">
         <v>35</v>
@@ -1432,7 +1468,7 @@
         <v>11201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C66" s="4">
         <v>24</v>
@@ -1446,7 +1482,7 @@
         <v>11202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C67" s="4">
         <v>24</v>
@@ -1474,7 +1510,7 @@
         <v>12102</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C69" s="4">
         <v>24</v>
@@ -1488,7 +1524,7 @@
         <v>12103</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C70" s="4">
         <v>24</v>
@@ -1516,7 +1552,7 @@
         <v>12202</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C72" s="4">
         <v>24</v>
@@ -1530,7 +1566,7 @@
         <v>12203</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C73" s="4">
         <v>24</v>
@@ -1544,7 +1580,7 @@
         <v>13101</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C74" s="4">
         <v>24</v>
@@ -1558,7 +1594,7 @@
         <v>13102</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C75" s="4">
         <v>24</v>
@@ -1572,7 +1608,7 @@
         <v>13103</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C76" s="4">
         <v>24</v>
@@ -1586,7 +1622,7 @@
         <v>13201</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C77" s="4">
         <v>24</v>
@@ -1600,7 +1636,7 @@
         <v>13202</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="C78" s="4">
         <v>24</v>
@@ -1614,7 +1650,7 @@
         <v>13203</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C79" s="4">
         <v>24</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FB9BCA-483F-4821-9867-4C53C4B3B3C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86820C98-97CA-4FD4-9FE4-15B5A62AF484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="49">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>1:9600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击点:击退距离系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_back_range</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -259,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -270,6 +282,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -550,1112 +563,1348 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="69.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.375" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
+      <c r="C1" s="1"/>
       <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" s="2"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>30000201</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2">
-        <v>70</v>
+      <c r="C5" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D5" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E5" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>30000601</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="2">
-        <v>70</v>
+      <c r="C6" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D6" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E6" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>30000301</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="2">
-        <v>70</v>
+      <c r="C7" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D7" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E7" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>30000701</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2">
-        <v>70</v>
+      <c r="C8" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D8" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E8" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>30000401</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="2">
-        <v>70</v>
+      <c r="C9" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D9" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E9" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>30000801</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2">
-        <v>70</v>
+      <c r="C10" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D10" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E10" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>30010101</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="2">
         <v>50</v>
       </c>
-      <c r="D11" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E11" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>30010102</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="2">
         <v>50</v>
       </c>
-      <c r="D12" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E12" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>100201011</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="2">
         <v>46</v>
       </c>
-      <c r="D13" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E13" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>100201021</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="2">
         <v>67</v>
       </c>
-      <c r="D14" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E14" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>100201031</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="2">
         <v>85</v>
       </c>
-      <c r="D15" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E15" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>30030101</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="2">
         <v>33</v>
       </c>
-      <c r="D16" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>30030102</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="2">
         <v>53</v>
       </c>
-      <c r="D17" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>30030103</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="2">
-        <v>17</v>
+      <c r="C18" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D18" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="E18" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>30030104</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="2">
-        <v>40</v>
+      <c r="C19" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D19" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>990101</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="2">
-        <v>70</v>
+      <c r="C20" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D20" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E20" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>990102</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="2">
-        <v>70</v>
+      <c r="C21" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D21" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E21" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>990201</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="2">
-        <v>70</v>
+      <c r="C22" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D22" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E22" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>990202</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="2">
-        <v>70</v>
+      <c r="C23" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D23" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E23" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>990301</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="2">
-        <v>70</v>
+      <c r="C24" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D24" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E24" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>990302</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="2">
-        <v>70</v>
+      <c r="C25" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D25" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E25" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>990401</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2">
-        <v>70</v>
+      <c r="C26" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D26" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E26" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>990402</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C27" s="2">
-        <v>70</v>
+      <c r="C27" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D27" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E27" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>990501</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C28" s="2">
-        <v>70</v>
+      <c r="C28" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D28" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E28" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>990502</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="2">
-        <v>70</v>
+      <c r="C29" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D29" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E29" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>10000801</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C30" s="2">
-        <v>70</v>
+      <c r="C30" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D30" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E30" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>10000802</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="2">
-        <v>70</v>
+      <c r="C31" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D31" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E31" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>10000803</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="2">
-        <v>70</v>
+      <c r="C32" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D32" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E32" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>10000901</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="2">
-        <v>70</v>
+      <c r="C33" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D33" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E33" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>10000902</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="2">
-        <v>70</v>
+      <c r="C34" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D34" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E34" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>10000903</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="2">
-        <v>70</v>
+      <c r="C35" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D35" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E35" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>10011001</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C36" s="2">
-        <v>70</v>
+      <c r="C36" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D36" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E36" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>10011002</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C37" s="2">
-        <v>70</v>
+      <c r="C37" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D37" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E37" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10011101</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="2">
-        <v>70</v>
+      <c r="C38" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D38" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E38" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10011102</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="2">
-        <v>70</v>
+      <c r="C39" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D39" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E39" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>10011201</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C40" s="2">
-        <v>70</v>
+      <c r="C40" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D40" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E40" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>10011202</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="2">
-        <v>70</v>
+      <c r="C41" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D41" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E41" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>10011301</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="2">
-        <v>70</v>
+      <c r="C42" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D42" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E42" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10011302</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C43" s="2">
-        <v>70</v>
+      <c r="C43" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D43" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E43" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>10011401</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="2">
-        <v>70</v>
+      <c r="C44" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D44" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E44" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>10011402</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C45" s="2">
-        <v>70</v>
+      <c r="C45" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D45" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E45" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>10011501</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="2">
-        <v>70</v>
+      <c r="C46" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D46" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E46" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>10011502</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C47" s="2">
-        <v>70</v>
+      <c r="C47" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D47" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E47" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>10011601</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C48" s="2">
-        <v>70</v>
+      <c r="C48" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D48" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E48" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>10011602</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="2">
-        <v>70</v>
+      <c r="C49" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D49" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E49" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>10001201</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="2">
-        <v>70</v>
+      <c r="C50" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D50" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E50" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>10001202</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C51" s="2">
-        <v>70</v>
+      <c r="C51" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D51" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E51" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>10001401</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C52" s="2">
-        <v>70</v>
+      <c r="C52" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D52" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E52" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>10001402</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="2">
-        <v>70</v>
+      <c r="C53" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D53" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="E53" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1001011</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="4">
-        <v>0</v>
+      <c r="C54" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E54" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1001021</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C55" s="4">
-        <v>0</v>
+      <c r="C55" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E55" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1002011</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C56" s="4">
-        <v>0</v>
+      <c r="C56" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1002021</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C57" s="4">
-        <v>0</v>
+      <c r="C57" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E57" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1004011</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C58" s="4">
-        <v>0</v>
+      <c r="C58" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1004021</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C59" s="4">
-        <v>0</v>
+      <c r="C59" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E59" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>3002011</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="4">
-        <v>0</v>
+      <c r="C60" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E60" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>3002021</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="4">
-        <v>0</v>
+      <c r="C61" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>14001011</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="4">
-        <v>0</v>
+      <c r="C62" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E62" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>14001021</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="4">
-        <v>0</v>
+      <c r="C63" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E63" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>11101</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="4">
         <v>35</v>
       </c>
-      <c r="D64" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>11102</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65" s="4">
         <v>35</v>
       </c>
-      <c r="D65" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>11201</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="4">
         <v>24</v>
       </c>
-      <c r="D66" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>11202</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="4">
         <v>24</v>
       </c>
-      <c r="D67" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E67" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>12101</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D68" s="4">
         <v>15</v>
       </c>
-      <c r="D68" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>12102</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="4">
         <v>24</v>
       </c>
-      <c r="D69" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>12103</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="4">
         <v>24</v>
       </c>
-      <c r="D70" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>12201</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D71" s="4">
         <v>24</v>
       </c>
-      <c r="D71" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>12202</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D72" s="4">
         <v>24</v>
       </c>
-      <c r="D72" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>12203</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D73" s="4">
         <v>24</v>
       </c>
-      <c r="D73" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>13101</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="4">
         <v>24</v>
       </c>
-      <c r="D74" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>13102</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="4">
         <v>24</v>
       </c>
-      <c r="D75" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>13103</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D76" s="4">
         <v>24</v>
       </c>
-      <c r="D76" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>13201</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77" s="4">
         <v>24</v>
       </c>
-      <c r="D77" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13202</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" s="4">
         <v>24</v>
       </c>
-      <c r="D78" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>13203</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D79" s="4">
         <v>24</v>
       </c>
-      <c r="D79" s="4">
+      <c r="E79" s="4">
         <v>40</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86820C98-97CA-4FD4-9FE4-15B5A62AF484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42401640-E0F2-4CD9-847D-A3A9E82C53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="48">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,54 +164,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:13400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:11000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:2500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:6500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2670</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5400_2:5000_3:5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:3600</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:9600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>打击点:击退距离系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -221,6 +181,42 @@
   </si>
   <si>
     <t>attack_back_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1750_2:2050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4400_2:3400_3:3700_4:2100_5:2100_6:1700_7:1900_8:2000_9:1900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2400_2:3400_3:2900_4:2250_5:2400_6:5200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -607,7 +603,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -624,7 +620,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -641,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2">
         <v>70</v>
@@ -658,7 +654,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2">
         <v>70</v>
@@ -675,7 +671,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2">
         <v>70</v>
@@ -692,7 +688,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2">
         <v>70</v>
@@ -709,7 +705,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2">
         <v>70</v>
@@ -726,7 +722,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2">
         <v>70</v>
@@ -743,7 +739,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D11" s="2">
         <v>50</v>
@@ -760,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2">
         <v>50</v>
@@ -777,7 +773,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>46</v>
@@ -794,7 +790,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
         <v>67</v>
@@ -811,7 +807,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2">
         <v>85</v>
@@ -828,7 +824,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>33</v>
@@ -845,7 +841,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2">
         <v>53</v>
@@ -862,7 +858,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2">
         <v>17</v>
@@ -879,7 +875,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2">
         <v>40</v>
@@ -896,7 +892,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
         <v>70</v>
@@ -913,7 +909,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D21" s="2">
         <v>70</v>
@@ -930,7 +926,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D22" s="2">
         <v>70</v>
@@ -947,7 +943,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
         <v>70</v>
@@ -964,7 +960,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D24" s="2">
         <v>70</v>
@@ -981,7 +977,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2">
         <v>70</v>
@@ -998,7 +994,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D26" s="2">
         <v>70</v>
@@ -1015,7 +1011,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D27" s="2">
         <v>70</v>
@@ -1032,7 +1028,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D28" s="2">
         <v>70</v>
@@ -1049,7 +1045,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2">
         <v>70</v>
@@ -1066,7 +1062,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2">
         <v>70</v>
@@ -1083,7 +1079,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D31" s="2">
         <v>70</v>
@@ -1100,7 +1096,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2">
         <v>70</v>
@@ -1117,7 +1113,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
         <v>70</v>
@@ -1134,7 +1130,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -1151,7 +1147,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2">
         <v>70</v>
@@ -1168,7 +1164,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D36" s="2">
         <v>70</v>
@@ -1185,7 +1181,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D37" s="2">
         <v>70</v>
@@ -1202,7 +1198,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D38" s="2">
         <v>70</v>
@@ -1219,7 +1215,7 @@
         <v>17</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2">
         <v>70</v>
@@ -1236,7 +1232,7 @@
         <v>17</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D40" s="2">
         <v>70</v>
@@ -1253,7 +1249,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D41" s="2">
         <v>70</v>
@@ -1270,7 +1266,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D42" s="2">
         <v>70</v>
@@ -1287,7 +1283,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
@@ -1304,7 +1300,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2">
         <v>70</v>
@@ -1321,7 +1317,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2">
         <v>70</v>
@@ -1338,7 +1334,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2">
         <v>70</v>
@@ -1355,7 +1351,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D47" s="2">
         <v>70</v>
@@ -1372,7 +1368,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2">
         <v>70</v>
@@ -1389,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D49" s="2">
         <v>70</v>
@@ -1406,7 +1402,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D50" s="2">
         <v>70</v>
@@ -1423,7 +1419,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D51" s="2">
         <v>70</v>
@@ -1440,7 +1436,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2">
         <v>70</v>
@@ -1457,7 +1453,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D53" s="2">
         <v>70</v>
@@ -1474,7 +1470,7 @@
         <v>27</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -1491,7 +1487,7 @@
         <v>27</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -1508,7 +1504,7 @@
         <v>27</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -1525,7 +1521,7 @@
         <v>28</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -1542,7 +1538,7 @@
         <v>29</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
@@ -1559,7 +1555,7 @@
         <v>30</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
@@ -1576,7 +1572,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
@@ -1593,7 +1589,7 @@
         <v>31</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -1610,7 +1606,7 @@
         <v>31</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -1627,7 +1623,7 @@
         <v>31</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
@@ -1637,14 +1633,14 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="A64" s="4">
         <v>11101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1654,14 +1650,14 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="A65" s="4">
         <v>11102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1671,14 +1667,14 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="A66" s="4">
         <v>11201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D66" s="4">
         <v>24</v>
@@ -1688,14 +1684,14 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="A67" s="4">
         <v>11202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D67" s="4">
         <v>24</v>
@@ -1705,31 +1701,31 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68">
+      <c r="A68" s="4">
+        <v>11203</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D68" s="4">
+        <v>24</v>
+      </c>
+      <c r="E68" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
         <v>12101</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D68" s="4">
-        <v>15</v>
-      </c>
-      <c r="E68" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69">
-        <v>12102</v>
-      </c>
       <c r="B69" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D69" s="4">
         <v>24</v>
@@ -1739,14 +1735,14 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70">
-        <v>12103</v>
+      <c r="A70" s="4">
+        <v>12102</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D70" s="4">
         <v>24</v>
@@ -1756,14 +1752,14 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>12201</v>
+      <c r="A71" s="4">
+        <v>12103</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D71" s="4">
         <v>24</v>
@@ -1773,139 +1769,122 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72">
+      <c r="A72" s="4">
+        <v>12201</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D72" s="4">
+        <v>14</v>
+      </c>
+      <c r="E72" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
         <v>12202</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D72" s="4">
+      <c r="B73" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="4">
+        <v>14</v>
+      </c>
+      <c r="E73" s="4">
         <v>24</v>
       </c>
-      <c r="E72" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A73">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
         <v>12203</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D73" s="4">
+      <c r="B74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D74" s="4">
+        <v>14</v>
+      </c>
+      <c r="E74" s="4">
         <v>24</v>
       </c>
-      <c r="E73" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>12204</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="4">
+        <v>7</v>
+      </c>
+      <c r="E75" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>12205</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" s="4">
+        <v>14</v>
+      </c>
+      <c r="E76" s="4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
         <v>13101</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D74" s="4">
-        <v>24</v>
-      </c>
-      <c r="E74" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75">
-        <v>13102</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D75" s="4">
-        <v>24</v>
-      </c>
-      <c r="E75" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A76">
-        <v>13103</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D76" s="4">
-        <v>24</v>
-      </c>
-      <c r="E76" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A77">
+      <c r="B77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" s="4">
+        <v>8</v>
+      </c>
+      <c r="E77" s="4">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" s="4">
         <v>13201</v>
       </c>
-      <c r="B77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D77" s="4">
-        <v>24</v>
-      </c>
-      <c r="E77" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A78">
-        <v>13202</v>
-      </c>
       <c r="B78" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D78" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E78" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A79">
-        <v>13203</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="4">
-        <v>24</v>
-      </c>
-      <c r="E79" s="4">
-        <v>40</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42401640-E0F2-4CD9-847D-A3A9E82C53AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78891DC3-153B-4859-966E-291BD8C9F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -218,6 +218,16 @@
   <si>
     <t>1:2400_2:3400_3:2900_4:2250_5:2400_6:5200</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5500_2:4250_3:4625_4:2625_5:2625_6:2125_7:2375_8:2500_9:2375</t>
+  </si>
+  <si>
+    <t>1:3000_2:4250_3:3625_4:2800_5:3000_6:6500</t>
   </si>
 </sst>
 </file>
@@ -1640,7 +1650,7 @@
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1657,7 +1667,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1674,7 +1684,7 @@
         <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D66" s="4">
         <v>24</v>
@@ -1691,7 +1701,7 @@
         <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D67" s="4">
         <v>24</v>
@@ -1708,7 +1718,7 @@
         <v>33</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D68" s="4">
         <v>24</v>
@@ -1861,7 +1871,7 @@
         <v>46</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D77" s="4">
         <v>8</v>
@@ -1878,7 +1888,7 @@
         <v>47</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D78" s="4">
         <v>12</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78891DC3-153B-4859-966E-291BD8C9F594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE2E0EE-E892-4767-9216-318CC214764B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -220,14 +220,30 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:1600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:5500_2:4250_3:4625_4:2625_5:2625_6:2125_7:2375_8:2500_9:2375</t>
   </si>
   <si>
     <t>1:3000_2:4250_3:3625_4:2800_5:3000_6:6500</t>
+  </si>
+  <si>
+    <t>1:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2250_2:2500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1650,7 +1666,7 @@
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1667,7 +1683,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1684,7 +1700,7 @@
         <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D66" s="4">
         <v>24</v>
@@ -1701,7 +1717,7 @@
         <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D67" s="4">
         <v>24</v>
@@ -1718,7 +1734,7 @@
         <v>33</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D68" s="4">
         <v>24</v>
@@ -1735,7 +1751,7 @@
         <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D69" s="4">
         <v>24</v>
@@ -1752,7 +1768,7 @@
         <v>32</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D70" s="4">
         <v>24</v>
@@ -1769,7 +1785,7 @@
         <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D71" s="4">
         <v>24</v>
@@ -1786,7 +1802,7 @@
         <v>43</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D72" s="4">
         <v>14</v>
@@ -1803,7 +1819,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D73" s="4">
         <v>14</v>
@@ -1820,7 +1836,7 @@
         <v>34</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D74" s="4">
         <v>14</v>
@@ -1837,7 +1853,7 @@
         <v>44</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D75" s="4">
         <v>7</v>
@@ -1854,7 +1870,7 @@
         <v>45</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D76" s="4">
         <v>14</v>
@@ -1871,7 +1887,7 @@
         <v>46</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D77" s="4">
         <v>8</v>
@@ -1888,7 +1904,7 @@
         <v>47</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D78" s="4">
         <v>12</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE2E0EE-E892-4767-9216-318CC214764B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D5C914-0BBF-409F-8C86-85C85D708DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="56">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -220,12 +220,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:5500_2:4250_3:4625_4:2625_5:2625_6:2125_7:2375_8:2500_9:2375</t>
-  </si>
-  <si>
-    <t>1:3000_2:4250_3:3625_4:2800_5:3000_6:6500</t>
-  </si>
-  <si>
     <t>1:6000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -238,11 +232,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:2250_2:2500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:5250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000_2:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5500_2:4250_3:4625_4:3200_5:3200_6:3200_7:3200_8:3200_9:3200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4000_2:5000_3:4500_4:4000_5:4000_6:6500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1666,7 +1672,7 @@
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1683,7 +1689,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1700,7 +1706,7 @@
         <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D66" s="4">
         <v>24</v>
@@ -1717,7 +1723,7 @@
         <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D67" s="4">
         <v>24</v>
@@ -1802,7 +1808,7 @@
         <v>43</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D72" s="4">
         <v>14</v>
@@ -1819,7 +1825,7 @@
         <v>35</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D73" s="4">
         <v>14</v>
@@ -1836,7 +1842,7 @@
         <v>34</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D74" s="4">
         <v>14</v>
@@ -1853,7 +1859,7 @@
         <v>44</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D75" s="4">
         <v>7</v>
@@ -1870,7 +1876,7 @@
         <v>45</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D76" s="4">
         <v>14</v>
@@ -1887,7 +1893,7 @@
         <v>46</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D77" s="4">
         <v>8</v>
@@ -1904,7 +1910,7 @@
         <v>47</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D78" s="4">
         <v>12</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D5C914-0BBF-409F-8C86-85C85D708DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD44D33-010E-46BC-80C9-68C1CB23245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -212,14 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4400_2:3400_3:3700_4:2100_5:2100_6:1700_7:1900_8:2000_9:1900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2400_2:3400_3:2900_4:2250_5:2400_6:5200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:6000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -244,11 +236,59 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:5500_2:4250_3:4625_4:3200_5:3200_6:3200_7:3200_8:3200_9:3200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4000_2:5000_3:4500_4:4000_5:4000_6:6500</t>
+    <t>1:4100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1800_2:1800_3:1800_4:1800_5:1800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2400_2:2400_3:2400_4:2400_5:2400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -591,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1672,7 +1712,7 @@
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1689,7 +1729,7 @@
         <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1706,7 +1746,7 @@
         <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D66" s="4">
         <v>24</v>
@@ -1723,7 +1763,7 @@
         <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D67" s="4">
         <v>24</v>
@@ -1808,7 +1848,7 @@
         <v>43</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D72" s="4">
         <v>14</v>
@@ -1859,7 +1899,7 @@
         <v>44</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D75" s="4">
         <v>7</v>
@@ -1876,7 +1916,7 @@
         <v>45</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D76" s="4">
         <v>14</v>
@@ -1890,33 +1930,169 @@
         <v>13101</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D77" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E77" s="4">
-        <v>120</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>13201</v>
+        <v>13102</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D78" s="4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
-        <v>120</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" s="4">
+        <v>13103</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79" s="4">
+        <v>8</v>
+      </c>
+      <c r="E79" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
+        <v>13104</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D80" s="4">
+        <v>10</v>
+      </c>
+      <c r="E80" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="4">
+        <v>13201</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10</v>
+      </c>
+      <c r="E81" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
+        <v>13202</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="4">
+        <v>10</v>
+      </c>
+      <c r="E82" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" s="4">
+        <v>13203</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D83" s="4">
+        <v>10</v>
+      </c>
+      <c r="E83" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" s="4">
+        <v>13204</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D84" s="4">
+        <v>10</v>
+      </c>
+      <c r="E84" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" s="4">
+        <v>13205</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D85" s="4">
+        <v>10</v>
+      </c>
+      <c r="E85" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>13206</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="4">
+        <v>20</v>
+      </c>
+      <c r="E86" s="4">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD44D33-010E-46BC-80C9-68C1CB23245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0556ED99-F68C-499B-B213-3BF29A964AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,14 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:2500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>打击点:击退距离系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -188,26 +180,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:3500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:3800</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:1750_2:2050</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:4250</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -216,42 +192,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3000_2:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:4100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:1800_2:1800_3:1800_4:1800_5:1800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:4500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:6500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:2400_2:2400_3:2400_4:2400_5:2400</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -289,6 +237,50 @@
   </si>
   <si>
     <t>1:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:13300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2050_2:2450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2500_2:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -675,7 +667,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -692,7 +684,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -709,7 +701,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2">
         <v>70</v>
@@ -726,7 +718,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2">
         <v>70</v>
@@ -743,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2">
         <v>70</v>
@@ -760,7 +752,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2">
         <v>70</v>
@@ -777,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2">
         <v>70</v>
@@ -794,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2">
         <v>70</v>
@@ -811,7 +803,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2">
         <v>50</v>
@@ -828,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>50</v>
@@ -845,7 +837,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>46</v>
@@ -862,7 +854,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>67</v>
@@ -879,7 +871,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2">
         <v>85</v>
@@ -896,7 +888,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2">
         <v>33</v>
@@ -913,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2">
         <v>53</v>
@@ -930,7 +922,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2">
         <v>17</v>
@@ -947,7 +939,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2">
         <v>40</v>
@@ -964,7 +956,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2">
         <v>70</v>
@@ -981,7 +973,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2">
         <v>70</v>
@@ -998,7 +990,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2">
         <v>70</v>
@@ -1015,7 +1007,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2">
         <v>70</v>
@@ -1032,7 +1024,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2">
         <v>70</v>
@@ -1049,7 +1041,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2">
         <v>70</v>
@@ -1066,7 +1058,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D26" s="2">
         <v>70</v>
@@ -1083,7 +1075,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D27" s="2">
         <v>70</v>
@@ -1100,7 +1092,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2">
         <v>70</v>
@@ -1117,7 +1109,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29" s="2">
         <v>70</v>
@@ -1134,7 +1126,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2">
         <v>70</v>
@@ -1151,7 +1143,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
         <v>70</v>
@@ -1168,7 +1160,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2">
         <v>70</v>
@@ -1185,7 +1177,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2">
         <v>70</v>
@@ -1202,7 +1194,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -1219,7 +1211,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2">
         <v>70</v>
@@ -1236,7 +1228,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D36" s="2">
         <v>70</v>
@@ -1253,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2">
         <v>70</v>
@@ -1270,7 +1262,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2">
         <v>70</v>
@@ -1287,7 +1279,7 @@
         <v>17</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D39" s="2">
         <v>70</v>
@@ -1304,7 +1296,7 @@
         <v>17</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2">
         <v>70</v>
@@ -1321,7 +1313,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2">
         <v>70</v>
@@ -1338,7 +1330,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D42" s="2">
         <v>70</v>
@@ -1355,7 +1347,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
@@ -1372,7 +1364,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2">
         <v>70</v>
@@ -1389,7 +1381,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2">
         <v>70</v>
@@ -1406,7 +1398,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D46" s="2">
         <v>70</v>
@@ -1423,7 +1415,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D47" s="2">
         <v>70</v>
@@ -1440,7 +1432,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2">
         <v>70</v>
@@ -1457,7 +1449,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D49" s="2">
         <v>70</v>
@@ -1474,7 +1466,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D50" s="2">
         <v>70</v>
@@ -1491,7 +1483,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2">
         <v>70</v>
@@ -1508,7 +1500,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D52" s="2">
         <v>70</v>
@@ -1525,7 +1517,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D53" s="2">
         <v>70</v>
@@ -1542,7 +1534,7 @@
         <v>27</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -1559,7 +1551,7 @@
         <v>27</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -1576,7 +1568,7 @@
         <v>27</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -1593,7 +1585,7 @@
         <v>28</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -1610,7 +1602,7 @@
         <v>29</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
@@ -1627,7 +1619,7 @@
         <v>30</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
@@ -1644,7 +1636,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
@@ -1661,7 +1653,7 @@
         <v>31</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -1678,7 +1670,7 @@
         <v>31</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -1695,7 +1687,7 @@
         <v>31</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
@@ -1706,13 +1698,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>11101</v>
+        <v>21101</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1723,13 +1715,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>11102</v>
+        <v>21102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1740,16 +1732,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>11201</v>
+        <v>21201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D66" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E66" s="4">
         <v>40</v>
@@ -1757,16 +1749,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>11202</v>
+        <v>21202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D67" s="4">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E67" s="4">
         <v>40</v>
@@ -1774,16 +1766,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>11203</v>
+        <v>22101</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D68" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E68" s="4">
         <v>40</v>
@@ -1791,16 +1783,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>12101</v>
+        <v>22102</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D69" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E69" s="4">
         <v>40</v>
@@ -1808,16 +1800,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>12102</v>
+        <v>22103</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D70" s="4">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E70" s="4">
         <v>40</v>
@@ -1825,30 +1817,30 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>12103</v>
+        <v>22201</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="D71" s="4">
+        <v>14</v>
+      </c>
+      <c r="E71" s="4">
         <v>24</v>
-      </c>
-      <c r="E71" s="4">
-        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>12201</v>
+        <v>22202</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="D72" s="4">
         <v>14</v>
@@ -1859,10 +1851,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>12202</v>
+        <v>22203</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>32</v>
@@ -1876,16 +1868,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>12203</v>
+        <v>22204</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D74" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E74" s="4">
         <v>24</v>
@@ -1893,16 +1885,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>12204</v>
+        <v>22205</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D75" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E75" s="4">
         <v>24</v>
@@ -1910,30 +1902,30 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>12205</v>
+        <v>23101</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D76" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E76" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>13101</v>
+        <v>23102</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D77" s="4">
         <v>10</v>
@@ -1944,47 +1936,47 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>13102</v>
+        <v>23103</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D78" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E78" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>13103</v>
+        <v>23104</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D79" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>13104</v>
+        <v>23201</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D80" s="4">
         <v>10</v>
@@ -1995,13 +1987,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>13201</v>
+        <v>23202</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D81" s="4">
         <v>10</v>
@@ -2012,13 +2004,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>13202</v>
+        <v>23203</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D82" s="4">
         <v>10</v>
@@ -2029,13 +2021,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>13203</v>
+        <v>23204</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2046,13 +2038,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>13204</v>
+        <v>23205</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2063,35 +2055,18 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>13205</v>
+        <v>23206</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D85" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E85" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" s="4">
-        <v>13206</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D86" s="4">
-        <v>20</v>
-      </c>
-      <c r="E86" s="4">
         <v>20</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0556ED99-F68C-499B-B213-3BF29A964AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD44D33-010E-46BC-80C9-68C1CB23245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,6 +164,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:2500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>打击点:击退距离系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -180,10 +188,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:3500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:3800</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:1750_2:2050</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:4250</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -192,14 +216,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:4800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000_2:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:4100</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:1800_2:1800_3:1800_4:1800_5:1800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:4500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>1:6500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:2400_2:2400_3:2400_4:2400_5:2400</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,50 +289,6 @@
   </si>
   <si>
     <t>1:12000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:13300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:12500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2050_2:2450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2500_2:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -667,7 +675,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -684,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -701,7 +709,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2">
         <v>70</v>
@@ -718,7 +726,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2">
         <v>70</v>
@@ -735,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2">
         <v>70</v>
@@ -752,7 +760,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2">
         <v>70</v>
@@ -769,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2">
         <v>70</v>
@@ -786,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="2">
         <v>70</v>
@@ -803,7 +811,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" s="2">
         <v>50</v>
@@ -820,7 +828,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" s="2">
         <v>50</v>
@@ -837,7 +845,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D13" s="2">
         <v>46</v>
@@ -854,7 +862,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
         <v>67</v>
@@ -871,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" s="2">
         <v>85</v>
@@ -888,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2">
         <v>33</v>
@@ -905,7 +913,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D17" s="2">
         <v>53</v>
@@ -922,7 +930,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2">
         <v>17</v>
@@ -939,7 +947,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D19" s="2">
         <v>40</v>
@@ -956,7 +964,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
         <v>70</v>
@@ -973,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D21" s="2">
         <v>70</v>
@@ -990,7 +998,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D22" s="2">
         <v>70</v>
@@ -1007,7 +1015,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="2">
         <v>70</v>
@@ -1024,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D24" s="2">
         <v>70</v>
@@ -1041,7 +1049,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D25" s="2">
         <v>70</v>
@@ -1058,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D26" s="2">
         <v>70</v>
@@ -1075,7 +1083,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D27" s="2">
         <v>70</v>
@@ -1092,7 +1100,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D28" s="2">
         <v>70</v>
@@ -1109,7 +1117,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D29" s="2">
         <v>70</v>
@@ -1126,7 +1134,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D30" s="2">
         <v>70</v>
@@ -1143,7 +1151,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D31" s="2">
         <v>70</v>
@@ -1160,7 +1168,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2">
         <v>70</v>
@@ -1177,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D33" s="2">
         <v>70</v>
@@ -1194,7 +1202,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -1211,7 +1219,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D35" s="2">
         <v>70</v>
@@ -1228,7 +1236,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D36" s="2">
         <v>70</v>
@@ -1245,7 +1253,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D37" s="2">
         <v>70</v>
@@ -1262,7 +1270,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D38" s="2">
         <v>70</v>
@@ -1279,7 +1287,7 @@
         <v>17</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D39" s="2">
         <v>70</v>
@@ -1296,7 +1304,7 @@
         <v>17</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D40" s="2">
         <v>70</v>
@@ -1313,7 +1321,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D41" s="2">
         <v>70</v>
@@ -1330,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D42" s="2">
         <v>70</v>
@@ -1347,7 +1355,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
@@ -1364,7 +1372,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D44" s="2">
         <v>70</v>
@@ -1381,7 +1389,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D45" s="2">
         <v>70</v>
@@ -1398,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2">
         <v>70</v>
@@ -1415,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D47" s="2">
         <v>70</v>
@@ -1432,7 +1440,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D48" s="2">
         <v>70</v>
@@ -1449,7 +1457,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D49" s="2">
         <v>70</v>
@@ -1466,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D50" s="2">
         <v>70</v>
@@ -1483,7 +1491,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D51" s="2">
         <v>70</v>
@@ -1500,7 +1508,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D52" s="2">
         <v>70</v>
@@ -1517,7 +1525,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D53" s="2">
         <v>70</v>
@@ -1534,7 +1542,7 @@
         <v>27</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -1551,7 +1559,7 @@
         <v>27</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -1568,7 +1576,7 @@
         <v>27</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -1585,7 +1593,7 @@
         <v>28</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -1602,7 +1610,7 @@
         <v>29</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
@@ -1619,7 +1627,7 @@
         <v>30</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
@@ -1636,7 +1644,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
@@ -1653,7 +1661,7 @@
         <v>31</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -1670,7 +1678,7 @@
         <v>31</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -1687,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
@@ -1698,13 +1706,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>21101</v>
+        <v>11101</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1715,13 +1723,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>21102</v>
+        <v>11102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1732,16 +1740,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>21201</v>
+        <v>11201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D66" s="4">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E66" s="4">
         <v>40</v>
@@ -1749,16 +1757,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>21202</v>
+        <v>11202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D67" s="4">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E67" s="4">
         <v>40</v>
@@ -1766,16 +1774,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>22101</v>
+        <v>11203</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D68" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E68" s="4">
         <v>40</v>
@@ -1783,16 +1791,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>22102</v>
+        <v>12101</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D69" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E69" s="4">
         <v>40</v>
@@ -1800,16 +1808,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>22103</v>
+        <v>12102</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D70" s="4">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E70" s="4">
         <v>40</v>
@@ -1817,30 +1825,30 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>22201</v>
+        <v>12103</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="D71" s="4">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E71" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>22202</v>
+        <v>12201</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D72" s="4">
         <v>14</v>
@@ -1851,10 +1859,10 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>22203</v>
+        <v>12202</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>32</v>
@@ -1868,16 +1876,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>22204</v>
+        <v>12203</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D74" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E74" s="4">
         <v>24</v>
@@ -1885,16 +1893,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>22205</v>
+        <v>12204</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D75" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E75" s="4">
         <v>24</v>
@@ -1902,30 +1910,30 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>23101</v>
+        <v>12205</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D76" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E76" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>23102</v>
+        <v>13101</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D77" s="4">
         <v>10</v>
@@ -1936,47 +1944,47 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>23103</v>
+        <v>13102</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D78" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>23104</v>
+        <v>13103</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D79" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E79" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>23201</v>
+        <v>13104</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D80" s="4">
         <v>10</v>
@@ -1987,13 +1995,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>23202</v>
+        <v>13201</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D81" s="4">
         <v>10</v>
@@ -2004,13 +2012,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>23203</v>
+        <v>13202</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D82" s="4">
         <v>10</v>
@@ -2021,13 +2029,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>23204</v>
+        <v>13203</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2038,13 +2046,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>23205</v>
+        <v>13204</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2055,18 +2063,35 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>23206</v>
+        <v>13205</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D85" s="4">
+        <v>10</v>
+      </c>
+      <c r="E85" s="4">
         <v>20</v>
       </c>
-      <c r="E85" s="4">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>13206</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="4">
+        <v>20</v>
+      </c>
+      <c r="E86" s="4">
         <v>20</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0556ED99-F68C-499B-B213-3BF29A964AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A7BF7E-3270-4D12-8AC8-BEFC3BA8C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="66">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -281,6 +281,14 @@
   </si>
   <si>
     <t>1:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2500</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1766,13 +1774,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>22101</v>
+        <v>21301</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D68" s="4">
         <v>20</v>
@@ -1783,16 +1791,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>22102</v>
+        <v>21302</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D69" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E69" s="4">
         <v>40</v>
@@ -1800,16 +1808,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>22103</v>
+        <v>21303</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D70" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E70" s="4">
         <v>40</v>
@@ -1817,67 +1825,67 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>22201</v>
+        <v>22101</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D71" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E71" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>22202</v>
+        <v>22102</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D72" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E72" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>22203</v>
+        <v>22103</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D73" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E73" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>22204</v>
+        <v>22201</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D74" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E74" s="4">
         <v>24</v>
@@ -1885,13 +1893,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>22205</v>
+        <v>22202</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D75" s="4">
         <v>14</v>
@@ -1902,64 +1910,64 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>23101</v>
+        <v>22203</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D76" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E76" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>23102</v>
+        <v>22204</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D77" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>23103</v>
+        <v>22205</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D78" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E78" s="4">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>23104</v>
+        <v>23101</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D79" s="4">
         <v>10</v>
@@ -1970,13 +1978,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>23201</v>
+        <v>23102</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D80" s="4">
         <v>10</v>
@@ -1987,30 +1995,30 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>23202</v>
+        <v>23103</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D81" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E81" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>23203</v>
+        <v>23104</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D82" s="4">
         <v>10</v>
@@ -2021,13 +2029,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>23204</v>
+        <v>23201</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2038,13 +2046,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>23205</v>
+        <v>23202</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2055,18 +2063,69 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
+        <v>23203</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D85" s="4">
+        <v>10</v>
+      </c>
+      <c r="E85" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" s="4">
+        <v>23204</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D86" s="4">
+        <v>10</v>
+      </c>
+      <c r="E86" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="4">
+        <v>23205</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="4">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="4">
         <v>23206</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D88" s="4">
         <v>20</v>
       </c>
-      <c r="E85" s="4">
+      <c r="E88" s="4">
         <v>20</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD44D33-010E-46BC-80C9-68C1CB23245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A7BF7E-3270-4D12-8AC8-BEFC3BA8C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="66">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -164,131 +164,131 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>打击点:击退距离系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>attack_back_range</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2400_2:2400_3:2400_4:2400_5:2400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1800</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:13300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:3700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2050_2:2450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:2500_2:3000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:5300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:4200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1:2500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打击点:击退距离系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>attack_back_range</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:7200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1750_2:2050</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3000_2:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:5400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1800_2:1800_3:1800_4:1800_5:1800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:6500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2400_2:2400_3:2400_4:2400_5:2400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:9500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:4750</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1800</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -675,7 +675,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>24</v>
@@ -692,7 +692,7 @@
         <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>13</v>
@@ -709,7 +709,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2">
         <v>70</v>
@@ -726,7 +726,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2">
         <v>70</v>
@@ -743,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D7" s="2">
         <v>70</v>
@@ -760,7 +760,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D8" s="2">
         <v>70</v>
@@ -777,7 +777,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" s="2">
         <v>70</v>
@@ -794,7 +794,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2">
         <v>70</v>
@@ -811,7 +811,7 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D11" s="2">
         <v>50</v>
@@ -828,7 +828,7 @@
         <v>18</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>50</v>
@@ -845,7 +845,7 @@
         <v>25</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" s="2">
         <v>46</v>
@@ -862,7 +862,7 @@
         <v>26</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2">
         <v>67</v>
@@ -879,7 +879,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D15" s="2">
         <v>85</v>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D16" s="2">
         <v>33</v>
@@ -913,7 +913,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D17" s="2">
         <v>53</v>
@@ -930,7 +930,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D18" s="2">
         <v>17</v>
@@ -947,7 +947,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D19" s="2">
         <v>40</v>
@@ -964,7 +964,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D20" s="2">
         <v>70</v>
@@ -981,7 +981,7 @@
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D21" s="2">
         <v>70</v>
@@ -998,7 +998,7 @@
         <v>17</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D22" s="2">
         <v>70</v>
@@ -1015,7 +1015,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2">
         <v>70</v>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2">
         <v>70</v>
@@ -1049,7 +1049,7 @@
         <v>17</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D25" s="2">
         <v>70</v>
@@ -1066,7 +1066,7 @@
         <v>17</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D26" s="2">
         <v>70</v>
@@ -1083,7 +1083,7 @@
         <v>17</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D27" s="2">
         <v>70</v>
@@ -1100,7 +1100,7 @@
         <v>17</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D28" s="2">
         <v>70</v>
@@ -1117,7 +1117,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D29" s="2">
         <v>70</v>
@@ -1134,7 +1134,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D30" s="2">
         <v>70</v>
@@ -1151,7 +1151,7 @@
         <v>17</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D31" s="2">
         <v>70</v>
@@ -1168,7 +1168,7 @@
         <v>17</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2">
         <v>70</v>
@@ -1185,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2">
         <v>70</v>
@@ -1202,7 +1202,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2">
         <v>70</v>
@@ -1219,7 +1219,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2">
         <v>70</v>
@@ -1236,7 +1236,7 @@
         <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D36" s="2">
         <v>70</v>
@@ -1253,7 +1253,7 @@
         <v>17</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D37" s="2">
         <v>70</v>
@@ -1270,7 +1270,7 @@
         <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2">
         <v>70</v>
@@ -1287,7 +1287,7 @@
         <v>17</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D39" s="2">
         <v>70</v>
@@ -1304,7 +1304,7 @@
         <v>17</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D40" s="2">
         <v>70</v>
@@ -1321,7 +1321,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D41" s="2">
         <v>70</v>
@@ -1338,7 +1338,7 @@
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D42" s="2">
         <v>70</v>
@@ -1355,7 +1355,7 @@
         <v>17</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2">
         <v>70</v>
@@ -1372,7 +1372,7 @@
         <v>17</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D44" s="2">
         <v>70</v>
@@ -1389,7 +1389,7 @@
         <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2">
         <v>70</v>
@@ -1406,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D46" s="2">
         <v>70</v>
@@ -1423,7 +1423,7 @@
         <v>17</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D47" s="2">
         <v>70</v>
@@ -1440,7 +1440,7 @@
         <v>17</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2">
         <v>70</v>
@@ -1457,7 +1457,7 @@
         <v>17</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D49" s="2">
         <v>70</v>
@@ -1474,7 +1474,7 @@
         <v>17</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D50" s="2">
         <v>70</v>
@@ -1491,7 +1491,7 @@
         <v>17</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D51" s="2">
         <v>70</v>
@@ -1508,7 +1508,7 @@
         <v>17</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D52" s="2">
         <v>70</v>
@@ -1525,7 +1525,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D53" s="2">
         <v>70</v>
@@ -1542,7 +1542,7 @@
         <v>27</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D54" s="4">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>27</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D55" s="4">
         <v>0</v>
@@ -1576,7 +1576,7 @@
         <v>27</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D56" s="4">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>28</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D57" s="4">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>29</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D58" s="4">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>30</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D59" s="4">
         <v>0</v>
@@ -1644,7 +1644,7 @@
         <v>31</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D60" s="4">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>31</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D61" s="4">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>31</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D62" s="4">
         <v>0</v>
@@ -1695,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D63" s="4">
         <v>0</v>
@@ -1706,13 +1706,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>11101</v>
+        <v>21101</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="D64" s="4">
         <v>35</v>
@@ -1723,13 +1723,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>11102</v>
+        <v>21102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D65" s="4">
         <v>35</v>
@@ -1740,16 +1740,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>11201</v>
+        <v>21201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D66" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E66" s="4">
         <v>40</v>
@@ -1757,16 +1757,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>11202</v>
+        <v>21202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D67" s="4">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E67" s="4">
         <v>40</v>
@@ -1774,16 +1774,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>11203</v>
+        <v>21301</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D68" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E68" s="4">
         <v>40</v>
@@ -1791,16 +1791,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>12101</v>
+        <v>21302</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="D69" s="4">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E69" s="4">
         <v>40</v>
@@ -1808,16 +1808,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>12102</v>
+        <v>21303</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D70" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E70" s="4">
         <v>40</v>
@@ -1825,16 +1825,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>12103</v>
+        <v>22101</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D71" s="4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E71" s="4">
         <v>40</v>
@@ -1842,47 +1842,47 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>12201</v>
+        <v>22102</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D72" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E72" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>12202</v>
+        <v>22103</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D73" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E73" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>12203</v>
+        <v>22201</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D74" s="4">
         <v>14</v>
@@ -1893,16 +1893,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>12204</v>
+        <v>22202</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D75" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E75" s="4">
         <v>24</v>
@@ -1910,13 +1910,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>12205</v>
+        <v>22203</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D76" s="4">
         <v>14</v>
@@ -1927,64 +1927,64 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>13101</v>
+        <v>22204</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D77" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E77" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>13102</v>
+        <v>22205</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D78" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E78" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>13103</v>
+        <v>23101</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="D79" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E79" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>13104</v>
+        <v>23102</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D80" s="4">
         <v>10</v>
@@ -1995,30 +1995,30 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>13201</v>
+        <v>23103</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="D81" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E81" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>13202</v>
+        <v>23104</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D82" s="4">
         <v>10</v>
@@ -2029,13 +2029,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>13203</v>
+        <v>23201</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>13204</v>
+        <v>23202</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2063,13 +2063,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>13205</v>
+        <v>23203</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D85" s="4">
         <v>10</v>
@@ -2080,18 +2080,52 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
-        <v>13206</v>
+        <v>23204</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D86" s="4">
+        <v>10</v>
+      </c>
+      <c r="E86" s="4">
         <v>20</v>
       </c>
-      <c r="E86" s="4">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" s="4">
+        <v>23205</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D87" s="4">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D88" s="4">
+        <v>20</v>
+      </c>
+      <c r="E88" s="4">
         <v>20</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltx\Desktop\高宁剑\【地宫】正式内容\分支表格\体验服\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A7BF7E-3270-4D12-8AC8-BEFC3BA8C2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52412CB-6863-4A0A-8266-4AF51FA29380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4215" yWindow="3180" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="65">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -284,11 +284,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:4200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:2500</t>
+    <t>1:3200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1777,7 +1773,7 @@
         <v>21301</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>32</v>
@@ -1794,10 +1790,10 @@
         <v>21302</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D69" s="4">
         <v>15</v>
@@ -1811,7 +1807,7 @@
         <v>21303</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>33</v>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52412CB-6863-4A0A-8266-4AF51FA29380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E913B513-A114-43CB-9F4D-ABA45056D23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4215" yWindow="3180" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="69">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -285,6 +285,22 @@
   </si>
   <si>
     <t>1:3200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打击点:计算受击档位武力比系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kongfu_hit_time_ratio</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:7200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -627,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -635,9 +651,10 @@
     <col min="3" max="3" width="69.375" customWidth="1"/>
     <col min="4" max="4" width="19.375" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.75" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,8 +662,9 @@
       <c r="C1" s="1"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -662,8 +680,11 @@
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -679,8 +700,11 @@
       <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -696,8 +720,11 @@
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>30000201</v>
       </c>
@@ -713,8 +740,11 @@
       <c r="E5" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>30000601</v>
       </c>
@@ -730,8 +760,11 @@
       <c r="E6" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>30000301</v>
       </c>
@@ -747,8 +780,11 @@
       <c r="E7" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>30000701</v>
       </c>
@@ -764,8 +800,11 @@
       <c r="E8" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>30000401</v>
       </c>
@@ -781,8 +820,11 @@
       <c r="E9" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>30000801</v>
       </c>
@@ -798,8 +840,11 @@
       <c r="E10" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>30010101</v>
       </c>
@@ -815,8 +860,11 @@
       <c r="E11" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>30010102</v>
       </c>
@@ -832,8 +880,11 @@
       <c r="E12" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>100201011</v>
       </c>
@@ -849,8 +900,11 @@
       <c r="E13" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>100201021</v>
       </c>
@@ -866,8 +920,11 @@
       <c r="E14" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>100201031</v>
       </c>
@@ -883,8 +940,11 @@
       <c r="E15" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>30030101</v>
       </c>
@@ -900,8 +960,11 @@
       <c r="E16" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>30030102</v>
       </c>
@@ -917,8 +980,11 @@
       <c r="E17" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>30030103</v>
       </c>
@@ -934,8 +1000,11 @@
       <c r="E18" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>30030104</v>
       </c>
@@ -951,8 +1020,11 @@
       <c r="E19" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>990101</v>
       </c>
@@ -968,8 +1040,11 @@
       <c r="E20" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>990102</v>
       </c>
@@ -985,8 +1060,11 @@
       <c r="E21" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>990201</v>
       </c>
@@ -1002,8 +1080,11 @@
       <c r="E22" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>990202</v>
       </c>
@@ -1019,8 +1100,11 @@
       <c r="E23" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>990301</v>
       </c>
@@ -1036,8 +1120,11 @@
       <c r="E24" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>990302</v>
       </c>
@@ -1053,8 +1140,11 @@
       <c r="E25" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>990401</v>
       </c>
@@ -1070,8 +1160,11 @@
       <c r="E26" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>990402</v>
       </c>
@@ -1087,8 +1180,11 @@
       <c r="E27" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>990501</v>
       </c>
@@ -1104,8 +1200,11 @@
       <c r="E28" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>990502</v>
       </c>
@@ -1121,8 +1220,11 @@
       <c r="E29" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>10000801</v>
       </c>
@@ -1138,8 +1240,11 @@
       <c r="E30" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>10000802</v>
       </c>
@@ -1155,8 +1260,11 @@
       <c r="E31" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>10000803</v>
       </c>
@@ -1172,8 +1280,11 @@
       <c r="E32" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>10000901</v>
       </c>
@@ -1189,8 +1300,11 @@
       <c r="E33" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>10000902</v>
       </c>
@@ -1206,8 +1320,11 @@
       <c r="E34" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>10000903</v>
       </c>
@@ -1223,8 +1340,11 @@
       <c r="E35" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>10011001</v>
       </c>
@@ -1240,8 +1360,11 @@
       <c r="E36" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>10011002</v>
       </c>
@@ -1257,8 +1380,11 @@
       <c r="E37" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F37" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>10011101</v>
       </c>
@@ -1274,8 +1400,11 @@
       <c r="E38" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>10011102</v>
       </c>
@@ -1291,8 +1420,11 @@
       <c r="E39" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>10011201</v>
       </c>
@@ -1308,8 +1440,11 @@
       <c r="E40" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>10011202</v>
       </c>
@@ -1325,8 +1460,11 @@
       <c r="E41" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>10011301</v>
       </c>
@@ -1342,8 +1480,11 @@
       <c r="E42" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F42" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10011302</v>
       </c>
@@ -1359,8 +1500,11 @@
       <c r="E43" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F43" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>10011401</v>
       </c>
@@ -1376,8 +1520,11 @@
       <c r="E44" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F44" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>10011402</v>
       </c>
@@ -1393,8 +1540,11 @@
       <c r="E45" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>10011501</v>
       </c>
@@ -1410,8 +1560,11 @@
       <c r="E46" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>10011502</v>
       </c>
@@ -1427,8 +1580,11 @@
       <c r="E47" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>10011601</v>
       </c>
@@ -1444,8 +1600,11 @@
       <c r="E48" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>10011602</v>
       </c>
@@ -1461,8 +1620,11 @@
       <c r="E49" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F49" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>10001201</v>
       </c>
@@ -1478,8 +1640,11 @@
       <c r="E50" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>10001202</v>
       </c>
@@ -1495,8 +1660,11 @@
       <c r="E51" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F51" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>10001401</v>
       </c>
@@ -1512,8 +1680,11 @@
       <c r="E52" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F52" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>10001402</v>
       </c>
@@ -1529,8 +1700,11 @@
       <c r="E53" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1001011</v>
       </c>
@@ -1546,8 +1720,11 @@
       <c r="E54" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F54" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1001021</v>
       </c>
@@ -1563,8 +1740,11 @@
       <c r="E55" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F55" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1002011</v>
       </c>
@@ -1580,8 +1760,11 @@
       <c r="E56" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F56" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1002021</v>
       </c>
@@ -1597,8 +1780,11 @@
       <c r="E57" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F57" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1004011</v>
       </c>
@@ -1614,8 +1800,11 @@
       <c r="E58" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F58" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1004021</v>
       </c>
@@ -1631,8 +1820,11 @@
       <c r="E59" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>3002011</v>
       </c>
@@ -1648,8 +1840,11 @@
       <c r="E60" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>3002021</v>
       </c>
@@ -1665,8 +1860,11 @@
       <c r="E61" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>14001011</v>
       </c>
@@ -1682,8 +1880,11 @@
       <c r="E62" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F62" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>14001021</v>
       </c>
@@ -1699,8 +1900,11 @@
       <c r="E63" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>21101</v>
       </c>
@@ -1716,8 +1920,11 @@
       <c r="E64" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>21102</v>
       </c>
@@ -1733,118 +1940,139 @@
       <c r="E65" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
+        <v>21103</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="4">
+        <v>50</v>
+      </c>
+      <c r="E66" s="4">
+        <v>40</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
         <v>21201</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B67" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D67" s="4">
         <v>18</v>
       </c>
-      <c r="E66" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
+      <c r="E67" s="4">
+        <v>40</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
         <v>21202</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D68" s="4">
         <v>52</v>
       </c>
-      <c r="E67" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
+      <c r="E68" s="4">
+        <v>40</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
         <v>21301</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D69" s="4">
         <v>20</v>
       </c>
-      <c r="E68" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="E69" s="4">
+        <v>40</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
         <v>21302</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D70" s="4">
         <v>15</v>
       </c>
-      <c r="E69" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
+      <c r="E70" s="4">
+        <v>40</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
         <v>21303</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D70" s="4">
-        <v>35</v>
-      </c>
-      <c r="E70" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
+      <c r="D71" s="4">
+        <v>35</v>
+      </c>
+      <c r="E71" s="4">
+        <v>40</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
         <v>22101</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D71" s="4">
-        <v>20</v>
-      </c>
-      <c r="E71" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
-        <v>22102</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D72" s="4">
         <v>20</v>
@@ -1852,50 +2080,59 @@
       <c r="E72" s="4">
         <v>40</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
+        <v>22102</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D73" s="4">
+        <v>20</v>
+      </c>
+      <c r="E73" s="4">
+        <v>40</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
         <v>22103</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D74" s="4">
         <v>30</v>
       </c>
-      <c r="E73" s="4">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
+      <c r="E74" s="4">
+        <v>40</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
         <v>22201</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D74" s="4">
-        <v>14</v>
-      </c>
-      <c r="E74" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>22202</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D75" s="4">
         <v>14</v>
@@ -1903,16 +2140,19 @@
       <c r="E75" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F75" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>22203</v>
+        <v>22202</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D76" s="4">
         <v>14</v>
@@ -1920,67 +2160,79 @@
       <c r="E76" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F76" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>22204</v>
+        <v>22203</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="D77" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E77" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>22205</v>
+        <v>22204</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D78" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E78" s="4">
         <v>24</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F78" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
+        <v>22205</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D79" s="4">
+        <v>14</v>
+      </c>
+      <c r="E79" s="4">
+        <v>24</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
         <v>23101</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="D79" s="4">
-        <v>10</v>
-      </c>
-      <c r="E79" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
-        <v>23102</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D80" s="4">
         <v>10</v>
@@ -1988,50 +2240,59 @@
       <c r="E80" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F80" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
+        <v>23102</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D81" s="4">
+        <v>10</v>
+      </c>
+      <c r="E81" s="4">
+        <v>20</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
         <v>23103</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D82" s="4">
         <v>8</v>
       </c>
-      <c r="E81" s="4">
+      <c r="E82" s="4">
         <v>60</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
+      <c r="F82" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="4">
         <v>23104</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="D82" s="4">
-        <v>10</v>
-      </c>
-      <c r="E82" s="4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" s="4">
-        <v>23201</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2039,16 +2300,19 @@
       <c r="E83" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F83" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>23202</v>
+        <v>23201</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2056,16 +2320,19 @@
       <c r="E84" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F84" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>23203</v>
+        <v>23202</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D85" s="4">
         <v>10</v>
@@ -2073,16 +2340,19 @@
       <c r="E85" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F85" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
-        <v>23204</v>
+        <v>23203</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D86" s="4">
         <v>10</v>
@@ -2090,16 +2360,19 @@
       <c r="E86" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F86" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
-        <v>23205</v>
+        <v>23204</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D87" s="4">
         <v>10</v>
@@ -2107,26 +2380,53 @@
       <c r="E87" s="4">
         <v>20</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F87" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
-        <v>23206</v>
+        <v>23205</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D88" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E88" s="4">
         <v>20</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D89" s="4">
+        <v>20</v>
+      </c>
+      <c r="E89" s="4">
+        <v>20</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E913B513-A114-43CB-9F4D-ABA45056D23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82544577-5986-41BA-B158-EAE0D8DD8969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="68">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -297,10 +297,6 @@
   </si>
   <si>
     <t>1:7200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1921,7 +1917,7 @@
         <v>40</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
@@ -1941,7 +1937,7 @@
         <v>40</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
@@ -1961,7 +1957,7 @@
         <v>40</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82544577-5986-41BA-B158-EAE0D8DD8969}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA13290-2FC2-4C2E-8B74-8B49D41CE0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="70">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -297,6 +297,14 @@
   </si>
   <si>
     <t>1:7200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:15000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:6000_2:11000_3:13000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1901,137 +1909,137 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>21101</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>18</v>
+      <c r="A64">
+        <v>16001001</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D64" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E64" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>21102</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>18</v>
+      <c r="A65">
+        <v>16001002</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D65" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E65" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>21103</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>63</v>
+      <c r="A66">
+        <v>16001003</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="D66" s="4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="E66" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>21201</v>
+        <v>21101</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D67" s="4">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E67" s="4">
         <v>40</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>21202</v>
+        <v>21102</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="D68" s="4">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E68" s="4">
         <v>40</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>21301</v>
+        <v>21103</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D69" s="4">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E69" s="4">
         <v>40</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>21302</v>
+        <v>21201</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="D70" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E70" s="4">
         <v>40</v>
@@ -2042,16 +2050,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>21303</v>
+        <v>21202</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D71" s="4">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E71" s="4">
         <v>40</v>
@@ -2062,13 +2070,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>22101</v>
+        <v>21301</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D72" s="4">
         <v>20</v>
@@ -2082,16 +2090,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>22102</v>
+        <v>21302</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D73" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E73" s="4">
         <v>40</v>
@@ -2102,7 +2110,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
-        <v>22103</v>
+        <v>21303</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>58</v>
@@ -2111,7 +2119,7 @@
         <v>33</v>
       </c>
       <c r="D74" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E74" s="4">
         <v>40</v>
@@ -2122,19 +2130,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
-        <v>22201</v>
+        <v>22101</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D75" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E75" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>35</v>
@@ -2142,19 +2150,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
-        <v>22202</v>
+        <v>22102</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D76" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E76" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>35</v>
@@ -2162,19 +2170,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
-        <v>22203</v>
+        <v>22103</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D77" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E77" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>35</v>
@@ -2182,16 +2190,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
-        <v>22204</v>
+        <v>22201</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D78" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E78" s="4">
         <v>24</v>
@@ -2202,13 +2210,13 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>22205</v>
+        <v>22202</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="D79" s="4">
         <v>14</v>
@@ -2222,19 +2230,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
-        <v>23101</v>
+        <v>22203</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D80" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E80" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>35</v>
@@ -2242,19 +2250,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
-        <v>23102</v>
+        <v>22204</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D81" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E81" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>35</v>
@@ -2262,19 +2270,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
-        <v>23103</v>
+        <v>22205</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D82" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E82" s="4">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>35</v>
@@ -2282,13 +2290,13 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
-        <v>23104</v>
+        <v>23101</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D83" s="4">
         <v>10</v>
@@ -2302,13 +2310,13 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
-        <v>23201</v>
+        <v>23102</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D84" s="4">
         <v>10</v>
@@ -2322,19 +2330,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
-        <v>23202</v>
+        <v>23103</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D85" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E85" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>35</v>
@@ -2342,13 +2350,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
-        <v>23203</v>
+        <v>23104</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D86" s="4">
         <v>10</v>
@@ -2362,13 +2370,13 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
-        <v>23204</v>
+        <v>23201</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D87" s="4">
         <v>10</v>
@@ -2382,13 +2390,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
-        <v>23205</v>
+        <v>23202</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="D88" s="4">
         <v>10</v>
@@ -2402,21 +2410,81 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
-        <v>23206</v>
+        <v>23203</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D89" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4">
         <v>20</v>
       </c>
       <c r="F89" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="4">
+        <v>23204</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" s="4">
+        <v>10</v>
+      </c>
+      <c r="E90" s="4">
+        <v>20</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="4">
+        <v>23205</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D91" s="4">
+        <v>10</v>
+      </c>
+      <c r="E91" s="4">
+        <v>20</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D92" s="4">
+        <v>20</v>
+      </c>
+      <c r="E92" s="4">
+        <v>20</v>
+      </c>
+      <c r="F92" s="6" t="s">
         <v>35</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0858E3A6-CA27-47A7-8EF8-8C30CA41DF53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E7A3D9-F779-495C-A3F6-0FAB5E029AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="69">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -297,6 +297,14 @@
   </si>
   <si>
     <t>1:13700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:14300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:12000_2:12000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1245,10 +1253,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
-        <v>8001001</v>
+        <v>7001001</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>21</v>
@@ -1265,10 +1273,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
-        <v>8001002</v>
+        <v>7001002</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>21</v>
@@ -1285,10 +1293,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
-        <v>11001001</v>
+        <v>7003001</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>21</v>
@@ -1305,10 +1313,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
-        <v>11001002</v>
+        <v>7003002</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>21</v>
@@ -1325,10 +1333,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
-        <v>11002001</v>
+        <v>8001001</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>21</v>
@@ -1345,10 +1353,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
-        <v>11002002</v>
+        <v>8001002</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>21</v>
@@ -1365,10 +1373,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
-        <v>13003001</v>
+        <v>11001001</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>21</v>
@@ -1385,10 +1393,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
-        <v>13003002</v>
+        <v>11001002</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>21</v>
@@ -1405,10 +1413,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
-        <v>16001001</v>
+        <v>11002001</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>21</v>
@@ -1425,10 +1433,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
-        <v>16001002</v>
+        <v>11002002</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>21</v>
@@ -1445,99 +1453,99 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
+        <v>13003001</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="4">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4">
+        <v>0</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="7">
+        <v>13003002</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="4">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4">
+        <v>0</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="7">
+        <v>16001001</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="4">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="7">
+        <v>16001002</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="4">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4">
+        <v>0</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="7">
         <v>16001003</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B45" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="4">
-        <v>0</v>
-      </c>
-      <c r="E41" s="4">
-        <v>0</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>21101</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="4">
-        <v>35</v>
-      </c>
-      <c r="E42" s="4">
-        <v>40</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
-        <v>21102</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="4">
-        <v>35</v>
-      </c>
-      <c r="E43" s="4">
-        <v>40</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
-        <v>21103</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="4">
-        <v>50</v>
-      </c>
-      <c r="E44" s="4">
-        <v>40</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
-        <v>21201</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>18</v>
+      <c r="C45" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D45" s="4">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E45" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>21</v>
@@ -1545,76 +1553,76 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>21202</v>
+        <v>21101</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="D46" s="4">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E46" s="4">
         <v>40</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>21301</v>
+        <v>21102</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D47" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E47" s="4">
         <v>40</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>21302</v>
+        <v>21103</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D48" s="4">
         <v>50</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" s="4">
-        <v>15</v>
       </c>
       <c r="E48" s="4">
         <v>40</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>21303</v>
+        <v>21201</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" s="4">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="E49" s="4">
         <v>40</v>
@@ -1625,16 +1633,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>22101</v>
+        <v>21202</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="D50" s="4">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E50" s="4">
         <v>40</v>
@@ -1645,13 +1653,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>22102</v>
+        <v>21301</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D51" s="4">
         <v>20</v>
@@ -1665,16 +1673,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>22103</v>
+        <v>21302</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D52" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E52" s="4">
         <v>40</v>
@@ -1685,19 +1693,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>22201</v>
+        <v>21303</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D53" s="4">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E53" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>21</v>
@@ -1705,19 +1713,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>22202</v>
+        <v>22101</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="D54" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E54" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>21</v>
@@ -1725,19 +1733,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>22203</v>
+        <v>22102</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D55" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E55" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>21</v>
@@ -1745,19 +1753,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>22204</v>
+        <v>22103</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="D56" s="4">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E56" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>21</v>
@@ -1765,13 +1773,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>22205</v>
+        <v>22201</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D57" s="4">
         <v>14</v>
@@ -1785,19 +1793,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>23101</v>
+        <v>22202</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D58" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E58" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>21</v>
@@ -1805,19 +1813,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>23102</v>
+        <v>22203</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="D59" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E59" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>21</v>
@@ -1825,19 +1833,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>23103</v>
+        <v>22204</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="D60" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E60" s="4">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>21</v>
@@ -1845,19 +1853,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>23104</v>
+        <v>22205</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D61" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E61" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>21</v>
@@ -1865,13 +1873,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>23201</v>
+        <v>23101</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D62" s="4">
         <v>10</v>
@@ -1885,13 +1893,13 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>23202</v>
+        <v>23102</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D63" s="4">
         <v>10</v>
@@ -1905,19 +1913,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>23203</v>
+        <v>23103</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D64" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E64" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>21</v>
@@ -1925,13 +1933,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>23204</v>
+        <v>23104</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D65" s="4">
         <v>10</v>
@@ -1945,13 +1953,13 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>23205</v>
+        <v>23201</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D66" s="4">
         <v>10</v>
@@ -1965,21 +1973,101 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>23206</v>
+        <v>23202</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D67" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>20</v>
       </c>
       <c r="F67" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>23203</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="4">
+        <v>10</v>
+      </c>
+      <c r="E68" s="4">
+        <v>20</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>23204</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D69" s="4">
+        <v>10</v>
+      </c>
+      <c r="E69" s="4">
+        <v>20</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>23205</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="4">
+        <v>10</v>
+      </c>
+      <c r="E70" s="4">
+        <v>20</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D71" s="4">
+        <v>20</v>
+      </c>
+      <c r="E71" s="4">
+        <v>20</v>
+      </c>
+      <c r="F71" s="6" t="s">
         <v>21</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E7A3D9-F779-495C-A3F6-0FAB5E029AA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A532FE-768D-46DB-9F13-157E46933F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="68">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -256,26 +256,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:19700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:22000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:11200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:15200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:21700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:12300</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,27 +264,43 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:16600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:11300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:15300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1:13700</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1:14300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1:12000_2:12000</t>
+    <t>1:13000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:11000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:16000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:19000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:16300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9900_2:10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:14200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:9700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1:8300</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -312,7 +308,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +329,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -355,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -368,6 +372,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -650,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -736,7 +743,7 @@
         <v>1001001</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>21</v>
@@ -756,7 +763,7 @@
         <v>1001002</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>21</v>
@@ -776,7 +783,7 @@
         <v>1002001</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>21</v>
@@ -796,7 +803,7 @@
         <v>1002002</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>21</v>
@@ -816,7 +823,7 @@
         <v>1003001</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>21</v>
@@ -836,7 +843,7 @@
         <v>1003002</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>21</v>
@@ -856,7 +863,7 @@
         <v>1004001</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>21</v>
@@ -876,7 +883,7 @@
         <v>1004002</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>21</v>
@@ -896,7 +903,7 @@
         <v>1005001</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
@@ -916,7 +923,7 @@
         <v>1005002</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>21</v>
@@ -936,7 +943,7 @@
         <v>1006001</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>21</v>
@@ -956,7 +963,7 @@
         <v>1006002</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>21</v>
@@ -1016,7 +1023,7 @@
         <v>3001001</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>21</v>
@@ -1036,7 +1043,7 @@
         <v>3001002</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>21</v>
@@ -1056,7 +1063,7 @@
         <v>3002001</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>21</v>
@@ -1076,7 +1083,7 @@
         <v>3002002</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>21</v>
@@ -1096,7 +1103,7 @@
         <v>3003001</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>21</v>
@@ -1116,7 +1123,7 @@
         <v>3003002</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>21</v>
@@ -1136,7 +1143,7 @@
         <v>4001001</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>21</v>
@@ -1176,7 +1183,7 @@
         <v>4002001</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>21</v>
@@ -1216,7 +1223,7 @@
         <v>4003001</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>21</v>
@@ -1236,7 +1243,7 @@
         <v>4003002</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>21</v>
@@ -1256,7 +1263,7 @@
         <v>7001001</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>21</v>
@@ -1276,7 +1283,7 @@
         <v>7001002</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>21</v>
@@ -1296,7 +1303,7 @@
         <v>7003001</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>21</v>
@@ -1316,7 +1323,7 @@
         <v>7003002</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>21</v>
@@ -1332,11 +1339,11 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="7">
-        <v>8001001</v>
+      <c r="A35" s="8">
+        <v>7002001</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>21</v>
@@ -1352,11 +1359,11 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="7">
-        <v>8001002</v>
+      <c r="A36" s="8">
+        <v>7002002</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>21</v>
@@ -1373,10 +1380,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
-        <v>11001001</v>
+        <v>8001001</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>21</v>
@@ -1393,10 +1400,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
-        <v>11001002</v>
+        <v>8001002</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>21</v>
@@ -1413,10 +1420,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
-        <v>11002001</v>
+        <v>11001001</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>21</v>
@@ -1433,10 +1440,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
-        <v>11002002</v>
+        <v>11001002</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>21</v>
@@ -1453,10 +1460,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
-        <v>13003001</v>
+        <v>11002001</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>21</v>
@@ -1473,10 +1480,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
-        <v>13003002</v>
+        <v>11002002</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>21</v>
@@ -1493,10 +1500,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
-        <v>16001001</v>
+        <v>13003001</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>21</v>
@@ -1513,10 +1520,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
-        <v>16001002</v>
+        <v>13003002</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>21</v>
@@ -1533,76 +1540,76 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
+        <v>16001001</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="7">
+        <v>16001002</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="4">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <v>0</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="7">
         <v>16001003</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B47" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D45" s="4">
-        <v>0</v>
-      </c>
-      <c r="E45" s="4">
-        <v>0</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
-        <v>21101</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="4">
-        <v>35</v>
-      </c>
-      <c r="E46" s="4">
-        <v>40</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
-        <v>21102</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>12</v>
+      <c r="C47" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D47" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E47" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>21103</v>
+        <v>21101</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D48" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E48" s="4">
         <v>40</v>
@@ -1613,56 +1620,56 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>21201</v>
+        <v>21102</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D49" s="4">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E49" s="4">
         <v>40</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>21202</v>
+        <v>21103</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D50" s="4">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" s="4">
         <v>40</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>21301</v>
+        <v>21201</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D51" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E51" s="4">
         <v>40</v>
@@ -1673,16 +1680,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>21302</v>
+        <v>21202</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D52" s="4">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E52" s="4">
         <v>40</v>
@@ -1693,16 +1700,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>21303</v>
+        <v>21301</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D53" s="4">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E53" s="4">
         <v>40</v>
@@ -1713,16 +1720,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>22101</v>
+        <v>21302</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D54" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E54" s="4">
         <v>40</v>
@@ -1733,16 +1740,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>22102</v>
+        <v>21303</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D55" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E55" s="4">
         <v>40</v>
@@ -1753,16 +1760,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>22103</v>
+        <v>22101</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D56" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E56" s="4">
         <v>40</v>
@@ -1773,19 +1780,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>22201</v>
+        <v>22102</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D57" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E57" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>21</v>
@@ -1793,19 +1800,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>22202</v>
+        <v>22103</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D58" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E58" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>21</v>
@@ -1813,13 +1820,13 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>22203</v>
+        <v>22201</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D59" s="4">
         <v>14</v>
@@ -1833,16 +1840,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>22204</v>
+        <v>22202</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="D60" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E60" s="4">
         <v>24</v>
@@ -1853,13 +1860,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>22205</v>
+        <v>22203</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D61" s="4">
         <v>14</v>
@@ -1873,19 +1880,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>23101</v>
+        <v>22204</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D62" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E62" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>21</v>
@@ -1893,19 +1900,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>23102</v>
+        <v>22205</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="D63" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E63" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>21</v>
@@ -1913,19 +1920,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>23103</v>
+        <v>23101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D64" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>21</v>
@@ -1933,13 +1940,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>23104</v>
+        <v>23102</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="D65" s="4">
         <v>10</v>
@@ -1953,19 +1960,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>23201</v>
+        <v>23103</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D66" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E66" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>21</v>
@@ -1973,13 +1980,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>23202</v>
+        <v>23104</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D67" s="4">
         <v>10</v>
@@ -1993,13 +2000,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>23203</v>
+        <v>23201</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D68" s="4">
         <v>10</v>
@@ -2013,13 +2020,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>23204</v>
+        <v>23202</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D69" s="4">
         <v>10</v>
@@ -2033,13 +2040,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>23205</v>
+        <v>23203</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D70" s="4">
         <v>10</v>
@@ -2053,21 +2060,61 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>23206</v>
+        <v>23204</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D71" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E71" s="4">
         <v>20</v>
       </c>
       <c r="F71" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>23205</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="4">
+        <v>10</v>
+      </c>
+      <c r="E72" s="4">
+        <v>20</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" s="4">
+        <v>20</v>
+      </c>
+      <c r="E73" s="4">
+        <v>20</v>
+      </c>
+      <c r="F73" s="6" t="s">
         <v>21</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A532FE-768D-46DB-9F13-157E46933F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C231DD93-B97E-40E7-A2AA-48D47C3220C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_act_info_v8" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="68">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -657,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" bestFit="1" customWidth="1"/>
@@ -1599,28 +1599,28 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
-        <v>21101</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>12</v>
+      <c r="A48" s="7">
+        <v>801001</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="D48" s="4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E48" s="4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>21102</v>
+        <v>21101</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>12</v>
@@ -1640,16 +1640,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>21103</v>
+        <v>21102</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="D50" s="4">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E50" s="4">
         <v>40</v>
@@ -1660,36 +1660,36 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>21201</v>
+        <v>21103</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D51" s="4">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E51" s="4">
         <v>40</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>21202</v>
+        <v>21201</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D52" s="4">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="E52" s="4">
         <v>40</v>
@@ -1700,16 +1700,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>21301</v>
+        <v>21202</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D53" s="4">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E53" s="4">
         <v>40</v>
@@ -1720,16 +1720,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>21302</v>
+        <v>21301</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D54" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54" s="4">
         <v>40</v>
@@ -1740,16 +1740,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>21303</v>
+        <v>21302</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D55" s="4">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E55" s="4">
         <v>40</v>
@@ -1760,16 +1760,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>22101</v>
+        <v>21303</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D56" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E56" s="4">
         <v>40</v>
@@ -1780,13 +1780,13 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>22102</v>
+        <v>22101</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D57" s="4">
         <v>20</v>
@@ -1800,16 +1800,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>22103</v>
+        <v>22102</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D58" s="4">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E58" s="4">
         <v>40</v>
@@ -1820,19 +1820,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>22201</v>
+        <v>22103</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D59" s="4">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E59" s="4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>21</v>
@@ -1840,13 +1840,13 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>22202</v>
+        <v>22201</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D60" s="4">
         <v>14</v>
@@ -1860,13 +1860,13 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>22203</v>
+        <v>22202</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D61" s="4">
         <v>14</v>
@@ -1880,16 +1880,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>22204</v>
+        <v>22203</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D62" s="4">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E62" s="4">
         <v>24</v>
@@ -1900,16 +1900,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>22205</v>
+        <v>22204</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D63" s="4">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E63" s="4">
         <v>24</v>
@@ -1920,19 +1920,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>23101</v>
+        <v>22205</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D64" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E64" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>21</v>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>23102</v>
+        <v>23101</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="D65" s="4">
         <v>10</v>
@@ -1960,19 +1960,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>23103</v>
+        <v>23102</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D66" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>21</v>
@@ -1980,19 +1980,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>23104</v>
+        <v>23103</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D67" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E67" s="4">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>21</v>
@@ -2000,13 +2000,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>23201</v>
+        <v>23104</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D68" s="4">
         <v>10</v>
@@ -2020,13 +2020,13 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>23202</v>
+        <v>23201</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D69" s="4">
         <v>10</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>23203</v>
+        <v>23202</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D70" s="4">
         <v>10</v>
@@ -2060,13 +2060,13 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>23204</v>
+        <v>23203</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D71" s="4">
         <v>10</v>
@@ -2080,13 +2080,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
-        <v>23205</v>
+        <v>23204</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D72" s="4">
         <v>10</v>
@@ -2100,21 +2100,41 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
-        <v>23206</v>
+        <v>23205</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D73" s="4">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E73" s="4">
         <v>20</v>
       </c>
       <c r="F73" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
+        <v>23206</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D74" s="4">
+        <v>20</v>
+      </c>
+      <c r="E74" s="4">
+        <v>20</v>
+      </c>
+      <c r="F74" s="6" t="s">
         <v>21</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6A451-020B-40E3-BF3F-FCF5B926EEEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB95822-4C13-4C22-8D03-ACB56DB3B750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="82">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -328,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -347,6 +347,9 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -622,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -1103,11 +1106,11 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>3001001</v>
+      <c r="A25" s="10">
+        <v>2004001</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1123,11 +1126,11 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>3001002</v>
+      <c r="A26" s="10">
+        <v>2004002</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
@@ -1144,10 +1147,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
-        <v>3002001</v>
+        <v>3001001</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1164,10 +1167,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
-        <v>3002002</v>
+        <v>3001002</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -1184,7 +1187,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
-        <v>3003001</v>
+        <v>3002001</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>22</v>
@@ -1204,7 +1207,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
-        <v>3003002</v>
+        <v>3002002</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>23</v>
@@ -1224,10 +1227,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
-        <v>4001001</v>
+        <v>3003001</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>17</v>
@@ -1244,10 +1247,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
-        <v>4001002</v>
+        <v>3003002</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>17</v>
@@ -1264,7 +1267,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
-        <v>4002001</v>
+        <v>4001001</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>24</v>
@@ -1284,7 +1287,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
-        <v>4002002</v>
+        <v>4001002</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>16</v>
@@ -1304,10 +1307,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>4003001</v>
+        <v>4002001</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>17</v>
@@ -1324,7 +1327,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
-        <v>4003002</v>
+        <v>4002002</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>16</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
-        <v>5001001</v>
+        <v>4003001</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>17</v>
@@ -1364,10 +1367,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
-        <v>5001002</v>
+        <v>4003002</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>17</v>
@@ -1384,7 +1387,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
-        <v>5003001</v>
+        <v>5001001</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>74</v>
@@ -1404,7 +1407,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
-        <v>5003001</v>
+        <v>5001002</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>28</v>
@@ -1424,7 +1427,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
-        <v>5004001</v>
+        <v>5003001</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>74</v>
@@ -1444,10 +1447,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
-        <v>5004002</v>
+        <v>5003001</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>17</v>
@@ -1464,10 +1467,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>6001001</v>
+        <v>5004001</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>17</v>
@@ -1484,10 +1487,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>6001002</v>
+        <v>5004002</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>17</v>
@@ -1504,10 +1507,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>7001001</v>
+        <v>6001001</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>17</v>
@@ -1524,10 +1527,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>7001002</v>
+        <v>6001002</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>17</v>
@@ -1544,7 +1547,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>7003001</v>
+        <v>7001001</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>26</v>
@@ -1564,7 +1567,7 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>7003002</v>
+        <v>7001002</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>27</v>
@@ -1584,7 +1587,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
-        <v>7002001</v>
+        <v>7003001</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>26</v>
@@ -1604,7 +1607,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
-        <v>7002002</v>
+        <v>7003002</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>27</v>
@@ -1624,10 +1627,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
-        <v>8001001</v>
+        <v>7002001</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>17</v>
@@ -1644,10 +1647,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
-        <v>8001002</v>
+        <v>7002002</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>17</v>
@@ -1664,10 +1667,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
-        <v>9001001</v>
+        <v>8001001</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>17</v>
@@ -1684,10 +1687,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
-        <v>9001002</v>
+        <v>8001002</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>17</v>
@@ -1704,7 +1707,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>9003001</v>
+        <v>9001001</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>78</v>
@@ -1724,7 +1727,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>9003002</v>
+        <v>9001002</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>79</v>
@@ -1744,10 +1747,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>11001001</v>
+        <v>9003001</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>17</v>
@@ -1764,10 +1767,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>11001002</v>
+        <v>9003002</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>17</v>
@@ -1784,7 +1787,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>11002001</v>
+        <v>11001001</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>30</v>
@@ -1804,7 +1807,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>11002002</v>
+        <v>11001002</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
@@ -1824,10 +1827,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>11003001</v>
+        <v>11002001</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>17</v>
@@ -1844,10 +1847,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>11003002</v>
+        <v>11002002</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>17</v>
@@ -1864,7 +1867,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>11004001</v>
+        <v>11003001</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>80</v>
@@ -1884,7 +1887,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>11004002</v>
+        <v>11003002</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>81</v>
@@ -1904,10 +1907,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>13003001</v>
+        <v>11004001</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>17</v>
@@ -1924,10 +1927,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
-        <v>13003002</v>
+        <v>11004002</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>17</v>
@@ -1944,10 +1947,10 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
-        <v>14001001</v>
+        <v>13003001</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C67" s="7" t="s">
         <v>17</v>
@@ -1964,10 +1967,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>14001002</v>
+        <v>13003002</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C68" s="7" t="s">
         <v>17</v>
@@ -1984,10 +1987,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
-        <v>16001001</v>
+        <v>14001001</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C69" s="7" t="s">
         <v>17</v>
@@ -2004,10 +2007,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
-        <v>16001002</v>
+        <v>14001002</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>17</v>
@@ -2024,10 +2027,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
-        <v>16001003</v>
+        <v>16001001</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>17</v>
@@ -2044,76 +2047,76 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
+        <v>16001002</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>16001003</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
         <v>801001</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B74" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="1">
-        <v>21101</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="1">
-        <v>35</v>
-      </c>
-      <c r="E73" s="1">
-        <v>40</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="1">
-        <v>21102</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>35</v>
+      <c r="C74" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="D74" s="1">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
-        <v>21103</v>
+        <v>21101</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D75" s="1">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E75" s="1">
         <v>40</v>
@@ -2124,56 +2127,56 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
-        <v>21201</v>
+        <v>21102</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D76" s="1">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E76" s="1">
         <v>40</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
-        <v>21202</v>
+        <v>21103</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D77" s="1">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E77" s="1">
         <v>40</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
-        <v>21301</v>
+        <v>21201</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D78" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E78" s="1">
         <v>40</v>
@@ -2184,16 +2187,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
-        <v>21302</v>
+        <v>21202</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D79" s="1">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="E79" s="1">
         <v>40</v>
@@ -2204,16 +2207,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
-        <v>21303</v>
+        <v>21301</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D80" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E80" s="1">
         <v>40</v>
@@ -2224,16 +2227,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
-        <v>22101</v>
+        <v>21302</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="D81" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E81" s="1">
         <v>40</v>
@@ -2244,16 +2247,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
-        <v>22102</v>
+        <v>21303</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D82" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E82" s="1">
         <v>40</v>
@@ -2264,16 +2267,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
-        <v>22103</v>
+        <v>22101</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D83" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E83" s="1">
         <v>40</v>
@@ -2284,19 +2287,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
-        <v>22201</v>
+        <v>22102</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D84" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>17</v>
@@ -2304,19 +2307,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
-        <v>22202</v>
+        <v>22103</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D85" s="1">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E85" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>17</v>
@@ -2324,13 +2327,13 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
-        <v>22203</v>
+        <v>22201</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D86" s="1">
         <v>14</v>
@@ -2344,16 +2347,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
-        <v>22204</v>
+        <v>22202</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D87" s="1">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E87" s="1">
         <v>24</v>
@@ -2364,13 +2367,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
-        <v>22205</v>
+        <v>22203</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D88" s="1">
         <v>14</v>
@@ -2384,19 +2387,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
-        <v>23101</v>
+        <v>22204</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D89" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E89" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>17</v>
@@ -2404,19 +2407,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
-        <v>23102</v>
+        <v>22205</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D90" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E90" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>17</v>
@@ -2424,19 +2427,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
-        <v>23103</v>
+        <v>23101</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D91" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E91" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>17</v>
@@ -2444,13 +2447,13 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
-        <v>23104</v>
+        <v>23102</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="D92" s="1">
         <v>10</v>
@@ -2464,19 +2467,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
-        <v>23201</v>
+        <v>23103</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D93" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>17</v>
@@ -2484,13 +2487,13 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
-        <v>23202</v>
+        <v>23104</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D94" s="1">
         <v>10</v>
@@ -2504,13 +2507,13 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
-        <v>23203</v>
+        <v>23201</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D95" s="1">
         <v>10</v>
@@ -2524,13 +2527,13 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
-        <v>23204</v>
+        <v>23202</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D96" s="1">
         <v>10</v>
@@ -2544,13 +2547,13 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>23205</v>
+        <v>23203</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D97" s="1">
         <v>10</v>
@@ -2564,16 +2567,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>23206</v>
+        <v>23204</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="D98" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E98" s="1">
         <v>20</v>
@@ -2583,22 +2586,62 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A99" s="6">
+      <c r="A99" s="1">
+        <v>23205</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D99" s="1">
+        <v>10</v>
+      </c>
+      <c r="E99" s="1">
+        <v>20</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>23206</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100" s="1">
+        <v>20</v>
+      </c>
+      <c r="E100" s="1">
+        <v>20</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="6">
         <v>24101</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B101" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C101" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D99" s="1">
-        <v>0</v>
-      </c>
-      <c r="E99" s="1">
-        <v>0</v>
-      </c>
-      <c r="F99" s="7" t="s">
+      <c r="D101" s="1">
+        <v>0</v>
+      </c>
+      <c r="E101" s="1">
+        <v>0</v>
+      </c>
+      <c r="F101" s="7" t="s">
         <v>17</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_act_info_v8【迷宫-动作配置】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB95822-4C13-4C22-8D03-ACB56DB3B750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E31BD2-DEB8-4982-B533-85B2871EAB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="86">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -279,13 +279,25 @@
   </si>
   <si>
     <t>1:27600</t>
+  </si>
+  <si>
+    <t>1:14000</t>
+  </si>
+  <si>
+    <t>1:18600</t>
+  </si>
+  <si>
+    <t>1:11600</t>
+  </si>
+  <si>
+    <t>1:32000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +314,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -347,7 +367,7 @@
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -625,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.5" customWidth="1"/>
@@ -1106,7 +1126,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="10">
+      <c r="A25" s="3">
         <v>2004001</v>
       </c>
       <c r="B25" s="5" t="s">
@@ -1126,7 +1146,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="10">
+      <c r="A26" s="3">
         <v>2004002</v>
       </c>
       <c r="B26" s="5" t="s">
@@ -1426,11 +1446,11 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
-        <v>5003001</v>
+      <c r="A41" s="10">
+        <v>5002001</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>17</v>
@@ -1446,11 +1466,11 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>5003001</v>
+      <c r="A42" s="10">
+        <v>5002002</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>17</v>
@@ -1467,7 +1487,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
-        <v>5004001</v>
+        <v>5003001</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>74</v>
@@ -1487,10 +1507,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
-        <v>5004002</v>
+        <v>5003001</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>17</v>
@@ -1507,10 +1527,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
-        <v>6001001</v>
+        <v>5004001</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>17</v>
@@ -1527,10 +1547,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>6001002</v>
+        <v>5004002</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>17</v>
@@ -1547,10 +1567,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
-        <v>7001001</v>
+        <v>6001001</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>17</v>
@@ -1567,10 +1587,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
-        <v>7001002</v>
+        <v>6001002</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>17</v>
@@ -1586,11 +1606,11 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
-        <v>7003001</v>
+      <c r="A49" s="10">
+        <v>6002001</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>17</v>
@@ -1606,11 +1626,11 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
-        <v>7003002</v>
+      <c r="A50" s="10">
+        <v>6002002</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>17</v>
@@ -1626,11 +1646,11 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
-        <v>7002001</v>
+      <c r="A51" s="10">
+        <v>6003001</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>17</v>
@@ -1646,11 +1666,11 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
-        <v>7002002</v>
+      <c r="A52" s="10">
+        <v>6003002</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>17</v>
@@ -1666,11 +1686,11 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
-        <v>8001001</v>
+      <c r="A53" s="10">
+        <v>6004001</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>17</v>
@@ -1686,11 +1706,11 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
-        <v>8001002</v>
+      <c r="A54" s="10">
+        <v>6004002</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>17</v>
@@ -1707,10 +1727,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
-        <v>9001001</v>
+        <v>7001001</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>17</v>
@@ -1727,10 +1747,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
-        <v>9001002</v>
+        <v>7001002</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C56" s="7" t="s">
         <v>17</v>
@@ -1747,10 +1767,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>9003001</v>
+        <v>7003001</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>17</v>
@@ -1767,10 +1787,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
-        <v>9003002</v>
+        <v>7003002</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>17</v>
@@ -1787,10 +1807,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
-        <v>11001001</v>
+        <v>7002001</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>17</v>
@@ -1807,10 +1827,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
-        <v>11001002</v>
+        <v>7002002</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>17</v>
@@ -1827,10 +1847,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
-        <v>11002001</v>
+        <v>8001001</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>17</v>
@@ -1847,10 +1867,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
-        <v>11002002</v>
+        <v>8001002</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>17</v>
@@ -1867,10 +1887,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
-        <v>11003001</v>
+        <v>9001001</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>17</v>
@@ -1887,10 +1907,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
-        <v>11003002</v>
+        <v>9001002</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>17</v>
@@ -1907,10 +1927,10 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
-        <v>11004001</v>
+        <v>9003001</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>17</v>
@@ -1927,619 +1947,619 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
+        <v>9003002</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>0</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="10">
+        <v>10001001</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>0</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="10">
+        <v>10001002</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="10">
+        <v>10002001</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>0</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="10">
+        <v>10002002</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>0</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="10">
+        <v>10003001</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="10">
+        <v>10003002</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>0</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="10">
+        <v>10004001</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>0</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="10">
+        <v>10004002</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>0</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>11001001</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>0</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>11001002</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>0</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="4">
+        <v>11002001</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>0</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="4">
+        <v>11002002</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
+        <v>0</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="4">
+        <v>11003001</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>0</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="4">
+        <v>11003002</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="1">
+        <v>0</v>
+      </c>
+      <c r="E80" s="1">
+        <v>0</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="4">
+        <v>11004001</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D81" s="1">
+        <v>0</v>
+      </c>
+      <c r="E81" s="1">
+        <v>0</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="4">
         <v>11004002</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B82" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D66" s="1">
-        <v>0</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
+      <c r="C82" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D82" s="1">
+        <v>0</v>
+      </c>
+      <c r="E82" s="1">
+        <v>0</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="10">
+        <v>13001001</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="1">
+        <v>0</v>
+      </c>
+      <c r="E83" s="1">
+        <v>0</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="10">
+        <v>13001002</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="1">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1">
+        <v>0</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="10">
+        <v>13002001</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="1">
+        <v>0</v>
+      </c>
+      <c r="E85" s="1">
+        <v>0</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="10">
+        <v>13002002</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="1">
+        <v>0</v>
+      </c>
+      <c r="E86" s="1">
+        <v>0</v>
+      </c>
+      <c r="F86" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="4">
         <v>13003001</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B87" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="1">
-        <v>0</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
+      <c r="C87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="1">
+        <v>0</v>
+      </c>
+      <c r="E87" s="1">
+        <v>0</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="4">
         <v>13003002</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B88" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="1">
-        <v>0</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
+      <c r="C88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D88" s="1">
+        <v>0</v>
+      </c>
+      <c r="E88" s="1">
+        <v>0</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="10">
+        <v>13004001</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D89" s="1">
+        <v>0</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="10">
+        <v>13004002</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D90" s="1">
+        <v>0</v>
+      </c>
+      <c r="E90" s="1">
+        <v>0</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="4">
         <v>14001001</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B91" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C69" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="1">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
+      <c r="C91" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D91" s="1">
+        <v>0</v>
+      </c>
+      <c r="E91" s="1">
+        <v>0</v>
+      </c>
+      <c r="F91" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="4">
         <v>14001002</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B92" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C70" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="1">
-        <v>0</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
+      <c r="C92" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92" s="1">
+        <v>0</v>
+      </c>
+      <c r="E92" s="1">
+        <v>0</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="4">
         <v>16001001</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B93" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C71" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="1">
-        <v>0</v>
-      </c>
-      <c r="E71" s="1">
-        <v>0</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
+      <c r="C93" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D93" s="1">
+        <v>0</v>
+      </c>
+      <c r="E93" s="1">
+        <v>0</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="4">
         <v>16001002</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B94" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D72" s="1">
-        <v>0</v>
-      </c>
-      <c r="E72" s="1">
-        <v>0</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
+      <c r="C94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D94" s="1">
+        <v>0</v>
+      </c>
+      <c r="E94" s="1">
+        <v>0</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="4">
         <v>16001003</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B95" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D73" s="1">
-        <v>0</v>
-      </c>
-      <c r="E73" s="1">
-        <v>0</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
+      <c r="C95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D95" s="1">
+        <v>0</v>
+      </c>
+      <c r="E95" s="1">
+        <v>0</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="4">
         <v>801001</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B96" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C74" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="1">
-        <v>0</v>
-      </c>
-      <c r="E74" s="1">
-        <v>0</v>
-      </c>
-      <c r="F74" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A75" s="1">
-        <v>21101</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D75" s="1">
-        <v>35</v>
-      </c>
-      <c r="E75" s="1">
-        <v>40</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A76" s="1">
-        <v>21102</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D76" s="1">
-        <v>35</v>
-      </c>
-      <c r="E76" s="1">
-        <v>40</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="1">
-        <v>21103</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D77" s="1">
-        <v>50</v>
-      </c>
-      <c r="E77" s="1">
-        <v>40</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A78" s="1">
-        <v>21201</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="1">
-        <v>18</v>
-      </c>
-      <c r="E78" s="1">
-        <v>40</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A79" s="1">
-        <v>21202</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D79" s="1">
-        <v>52</v>
-      </c>
-      <c r="E79" s="1">
-        <v>40</v>
-      </c>
-      <c r="F79" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="1">
-        <v>21301</v>
-      </c>
-      <c r="B80" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D80" s="1">
-        <v>20</v>
-      </c>
-      <c r="E80" s="1">
-        <v>40</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A81" s="1">
-        <v>21302</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" s="1">
-        <v>15</v>
-      </c>
-      <c r="E81" s="1">
-        <v>40</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A82" s="1">
-        <v>21303</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" s="1">
-        <v>35</v>
-      </c>
-      <c r="E82" s="1">
-        <v>40</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A83" s="1">
-        <v>22101</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D83" s="1">
-        <v>20</v>
-      </c>
-      <c r="E83" s="1">
-        <v>40</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A84" s="1">
-        <v>22102</v>
-      </c>
-      <c r="B84" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D84" s="1">
-        <v>20</v>
-      </c>
-      <c r="E84" s="1">
-        <v>40</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A85" s="1">
-        <v>22103</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D85" s="1">
-        <v>30</v>
-      </c>
-      <c r="E85" s="1">
-        <v>40</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A86" s="1">
-        <v>22201</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D86" s="1">
-        <v>14</v>
-      </c>
-      <c r="E86" s="1">
-        <v>24</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A87" s="1">
-        <v>22202</v>
-      </c>
-      <c r="B87" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D87" s="1">
-        <v>14</v>
-      </c>
-      <c r="E87" s="1">
-        <v>24</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A88" s="1">
-        <v>22203</v>
-      </c>
-      <c r="B88" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D88" s="1">
-        <v>14</v>
-      </c>
-      <c r="E88" s="1">
-        <v>24</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A89" s="1">
-        <v>22204</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D89" s="1">
-        <v>7</v>
-      </c>
-      <c r="E89" s="1">
-        <v>24</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A90" s="1">
-        <v>22205</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D90" s="1">
-        <v>14</v>
-      </c>
-      <c r="E90" s="1">
-        <v>24</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A91" s="1">
-        <v>23101</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D91" s="1">
-        <v>10</v>
-      </c>
-      <c r="E91" s="1">
-        <v>20</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A92" s="1">
-        <v>23102</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D92" s="1">
-        <v>10</v>
-      </c>
-      <c r="E92" s="1">
-        <v>20</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A93" s="1">
-        <v>23103</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D93" s="1">
-        <v>8</v>
-      </c>
-      <c r="E93" s="1">
-        <v>60</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A94" s="1">
-        <v>23104</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D94" s="1">
-        <v>10</v>
-      </c>
-      <c r="E94" s="1">
-        <v>20</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A95" s="1">
-        <v>23201</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D95" s="1">
-        <v>10</v>
-      </c>
-      <c r="E95" s="1">
-        <v>20</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A96" s="1">
-        <v>23202</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>60</v>
+      <c r="C96" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="D96" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E96" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>17</v>
@@ -2547,101 +2567,541 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
-        <v>23203</v>
+        <v>21101</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="D97" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E97" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
-        <v>23204</v>
+        <v>21102</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D98" s="1">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="E98" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
-        <v>23205</v>
+        <v>21103</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="D99" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E99" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
+        <v>21201</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D100" s="1">
+        <v>18</v>
+      </c>
+      <c r="E100" s="1">
+        <v>40</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>21202</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D101" s="1">
+        <v>52</v>
+      </c>
+      <c r="E101" s="1">
+        <v>40</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>21301</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D102" s="1">
+        <v>20</v>
+      </c>
+      <c r="E102" s="1">
+        <v>40</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>21302</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103" s="1">
+        <v>15</v>
+      </c>
+      <c r="E103" s="1">
+        <v>40</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>21303</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" s="1">
+        <v>35</v>
+      </c>
+      <c r="E104" s="1">
+        <v>40</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>22101</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D105" s="1">
+        <v>20</v>
+      </c>
+      <c r="E105" s="1">
+        <v>40</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>22102</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D106" s="1">
+        <v>20</v>
+      </c>
+      <c r="E106" s="1">
+        <v>40</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>22103</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" s="1">
+        <v>30</v>
+      </c>
+      <c r="E107" s="1">
+        <v>40</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>22201</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" s="1">
+        <v>14</v>
+      </c>
+      <c r="E108" s="1">
+        <v>24</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>22202</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D109" s="1">
+        <v>14</v>
+      </c>
+      <c r="E109" s="1">
+        <v>24</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>22203</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D110" s="1">
+        <v>14</v>
+      </c>
+      <c r="E110" s="1">
+        <v>24</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>22204</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D111" s="1">
+        <v>7</v>
+      </c>
+      <c r="E111" s="1">
+        <v>24</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>22205</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D112" s="1">
+        <v>14</v>
+      </c>
+      <c r="E112" s="1">
+        <v>24</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>23101</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D113" s="1">
+        <v>10</v>
+      </c>
+      <c r="E113" s="1">
+        <v>20</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>23102</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114" s="1">
+        <v>10</v>
+      </c>
+      <c r="E114" s="1">
+        <v>20</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>23103</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D115" s="1">
+        <v>8</v>
+      </c>
+      <c r="E115" s="1">
+        <v>60</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>23104</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D116" s="1">
+        <v>10</v>
+      </c>
+      <c r="E116" s="1">
+        <v>20</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>23201</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D117" s="1">
+        <v>10</v>
+      </c>
+      <c r="E117" s="1">
+        <v>20</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>23202</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D118" s="1">
+        <v>10</v>
+      </c>
+      <c r="E118" s="1">
+        <v>20</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>23203</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D119" s="1">
+        <v>10</v>
+      </c>
+      <c r="E119" s="1">
+        <v>20</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>23204</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D120" s="1">
+        <v>10</v>
+      </c>
+      <c r="E120" s="1">
+        <v>20</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>23205</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D121" s="1">
+        <v>10</v>
+      </c>
+      <c r="E121" s="1">
+        <v>20</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
         <v>23206</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B122" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C122" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D122" s="1">
         <v>20</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E122" s="1">
         <v>20</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A101" s="6">
+      <c r="F122" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="6">
         <v>24101</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B123" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C123" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D101" s="1">
-        <v>0</v>
-      </c>
-      <c r="E101" s="1">
-        <v>0</v>
-      </c>
-      <c r="F101" s="7" t="s">
+      <c r="D123" s="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="1">
+        <v>0</v>
+      </c>
+      <c r="F123" s="7" t="s">
         <v>17</v>
       </c>
     </row>
